--- a/config/default/forms/app/pregnancy_danger_sign_follow_up.xlsx
+++ b/config/default/forms/app/pregnancy_danger_sign_follow_up.xlsx
@@ -1,17 +1,35 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\apoorva\cht-core\config\default\forms\app\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05A93119-1F43-4264-A64A-A3DC4E3AB1B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="15" windowWidth="20955" windowHeight="9720" activeTab="0"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId2"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId3"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId4"/>
-    <sheet name="choices-backup" sheetId="4" state="hidden" r:id="rId5"/>
+    <sheet name="survey" sheetId="1" r:id="rId1"/>
+    <sheet name="choices" sheetId="2" r:id="rId2"/>
+    <sheet name="settings" sheetId="3" r:id="rId3"/>
+    <sheet name="choices-backup" sheetId="4" state="hidden" r:id="rId4"/>
   </sheets>
-  <calcPr/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -21,7 +39,7 @@
     <author>tc={00B300CE-00C8-4377-9166-0080002800A0}</author>
   </authors>
   <commentList>
-    <comment ref="B39" authorId="0" xr:uid="{00B300CE-00C8-4377-9166-0080002800A0}">
+    <comment ref="B39" authorId="0" shapeId="0" xr:uid="{00B300CE-00C8-4377-9166-0080002800A0}">
       <text>
         <r>
           <rPr>
@@ -49,7 +67,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="323" uniqueCount="323">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="587" uniqueCount="323">
   <si>
     <t>type</t>
   </si>
@@ -153,7 +171,7 @@
     <t>cht::notes</t>
   </si>
   <si>
-    <t xml:space="preserve">begin group</t>
+    <t>begin group</t>
   </si>
   <si>
     <t>inputs</t>
@@ -162,7 +180,7 @@
     <t>NO_LABEL</t>
   </si>
   <si>
-    <t xml:space="preserve">./source = 'user'</t>
+    <t>./source = 'user'</t>
   </si>
   <si>
     <t>field-list</t>
@@ -183,22 +201,16 @@
     <t>source_id</t>
   </si>
   <si>
-    <t xml:space="preserve">Source ID</t>
+    <t>Source ID</t>
   </si>
   <si>
     <t>contact</t>
   </si>
   <si>
-    <t>db:person</t>
-  </si>
-  <si>
     <t>_id</t>
   </si>
   <si>
-    <t xml:space="preserve">What is the patient's name?</t>
-  </si>
-  <si>
-    <t>db-object</t>
+    <t>What is the patient's name?</t>
   </si>
   <si>
     <t>Name</t>
@@ -207,19 +219,19 @@
     <t>short_name</t>
   </si>
   <si>
-    <t xml:space="preserve">Short Name</t>
+    <t>Short Name</t>
   </si>
   <si>
     <t>patient_id</t>
   </si>
   <si>
-    <t xml:space="preserve">Patient ID</t>
+    <t>Patient ID</t>
   </si>
   <si>
     <t>date_of_birth</t>
   </si>
   <si>
-    <t xml:space="preserve">Date of Birth</t>
+    <t>Date of Birth</t>
   </si>
   <si>
     <t>sex</t>
@@ -231,22 +243,22 @@
     <t>parent</t>
   </si>
   <si>
-    <t xml:space="preserve">Parent ID</t>
+    <t>Parent ID</t>
   </si>
   <si>
     <t>chw_name</t>
   </si>
   <si>
-    <t xml:space="preserve">CHW name</t>
+    <t>CHW name</t>
   </si>
   <si>
     <t>phone</t>
   </si>
   <si>
-    <t xml:space="preserve">CHW phone</t>
-  </si>
-  <si>
-    <t xml:space="preserve">end group</t>
+    <t>CHW phone</t>
+  </si>
+  <si>
+    <t>end group</t>
   </si>
   <si>
     <t>calculate</t>
@@ -255,10 +267,10 @@
     <t>patient_age_in_years</t>
   </si>
   <si>
-    <t xml:space="preserve">floor( difference-in-months( ../inputs/contact/date_of_birth, today() ) div 12 )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Patient Age in Years</t>
+    <t>floor( difference-in-months( ../inputs/contact/date_of_birth, today() ) div 12 )</t>
+  </si>
+  <si>
+    <t>Patient Age in Years</t>
   </si>
   <si>
     <t>patient_uuid</t>
@@ -267,7 +279,7 @@
     <t>../inputs/contact/_id</t>
   </si>
   <si>
-    <t xml:space="preserve">Patient UUID</t>
+    <t>Patient UUID</t>
   </si>
   <si>
     <t>../inputs/contact/patient_id</t>
@@ -279,34 +291,34 @@
     <t>../inputs/contact/name</t>
   </si>
   <si>
-    <t xml:space="preserve">Patient Name</t>
+    <t>Patient Name</t>
   </si>
   <si>
     <t>patient_short_name</t>
   </si>
   <si>
-    <t xml:space="preserve">coalesce(../inputs/contact/short_name, ../danger_signs/custom_translations/custom_woman_label)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Patient Short Name</t>
+    <t>coalesce(../inputs/contact/short_name, ../danger_signs/custom_translations/custom_woman_label)</t>
+  </si>
+  <si>
+    <t>Patient Short Name</t>
   </si>
   <si>
     <t>patient_short_name_start</t>
   </si>
   <si>
-    <t xml:space="preserve">coalesce(../inputs/contact/short_name, ../danger_signs/custom_translations/custom_woman_start_label)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Patient Sort Name Start Label</t>
+    <t>coalesce(../inputs/contact/short_name, ../danger_signs/custom_translations/custom_woman_start_label)</t>
+  </si>
+  <si>
+    <t>Patient Sort Name Start Label</t>
   </si>
   <si>
     <t>t_danger_signs_referral_follow_up_date</t>
   </si>
   <si>
-    <t xml:space="preserve">date-time(decimal-date-time(today()) + 3)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Danger Signs Follow Up Date</t>
+    <t>date-time(decimal-date-time(today()) + 3)</t>
+  </si>
+  <si>
+    <t>Danger Signs Follow Up Date</t>
   </si>
   <si>
     <t>t_danger_signs_referral_follow_up</t>
@@ -315,31 +327,31 @@
     <t>../danger_signs/r_danger_sign_present</t>
   </si>
   <si>
-    <t xml:space="preserve">Danger Signs Present</t>
+    <t>Danger Signs Present</t>
   </si>
   <si>
     <t>pregnancy_uuid_ctx</t>
   </si>
   <si>
-    <t xml:space="preserve">if(instance('contact-summary')/context/pregnancy_uuid != '', instance('contact-summary')/context/pregnancy_uuid, .)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pregnancy UUID</t>
+    <t>if(instance('contact-summary')/context/pregnancy_uuid != '', instance('contact-summary')/context/pregnancy_uuid, .)</t>
+  </si>
+  <si>
+    <t>Pregnancy UUID</t>
   </si>
   <si>
     <t>danger_signs</t>
   </si>
   <si>
-    <t xml:space="preserve">Danger Sign Follow-up</t>
-  </si>
-  <si>
-    <t xml:space="preserve">select_one yes_no</t>
+    <t>Danger Sign Follow-up</t>
+  </si>
+  <si>
+    <t>select_one yes_no</t>
   </si>
   <si>
     <t>visit_confirm</t>
   </si>
   <si>
-    <t xml:space="preserve">Did ${patient_short_name} visit the health facility as recommended?</t>
+    <t>Did ${patient_short_name} visit the health facility as recommended?</t>
   </si>
   <si>
     <t>yes</t>
@@ -348,7 +360,7 @@
     <t>danger_sign_present</t>
   </si>
   <si>
-    <t xml:space="preserve">Is she still experiencing any danger signs?</t>
+    <t>Is she still experiencing any danger signs?</t>
   </si>
   <si>
     <t>note</t>
@@ -360,7 +372,7 @@
     <t xml:space="preserve">Great news! Please closely monitor her until her next scheduled ANC check-up at the health facility. </t>
   </si>
   <si>
-    <t xml:space="preserve">../danger_sign_present = 'no'</t>
+    <t>../danger_sign_present = 'no'</t>
   </si>
   <si>
     <t>refer_patient_note_1</t>
@@ -369,7 +381,7 @@
     <t xml:space="preserve">The mother should visit the health facility immediately if she is experiencing any of these danger signs. </t>
   </si>
   <si>
-    <t xml:space="preserve">../danger_sign_present = 'yes'</t>
+    <t>../danger_sign_present = 'yes'</t>
   </si>
   <si>
     <t>refer_patient_note_2</t>
@@ -387,7 +399,7 @@
     <t>vaginal_bleeding</t>
   </si>
   <si>
-    <t xml:space="preserve">Vaginal bleeding</t>
+    <t>Vaginal bleeding</t>
   </si>
   <si>
     <t>fits</t>
@@ -399,19 +411,19 @@
     <t>severe_abdominal_pain</t>
   </si>
   <si>
-    <t xml:space="preserve">Severe abdominal pain</t>
+    <t>Severe abdominal pain</t>
   </si>
   <si>
     <t>severe_headache</t>
   </si>
   <si>
-    <t xml:space="preserve">Severe headache</t>
+    <t>Severe headache</t>
   </si>
   <si>
     <t>very_pale</t>
   </si>
   <si>
-    <t xml:space="preserve">Very pale</t>
+    <t>Very pale</t>
   </si>
   <si>
     <t>fever</t>
@@ -423,25 +435,25 @@
     <t>reduced_or_no_fetal_movements</t>
   </si>
   <si>
-    <t xml:space="preserve">Reduced or no fetal movements</t>
+    <t>Reduced or no fetal movements</t>
   </si>
   <si>
     <t>breaking_water</t>
   </si>
   <si>
-    <t xml:space="preserve">Breaking of water</t>
+    <t>Breaking of water</t>
   </si>
   <si>
     <t>easily_tired</t>
   </si>
   <si>
-    <t xml:space="preserve">Getting tired easily</t>
+    <t>Getting tired easily</t>
   </si>
   <si>
     <t>face_hand_swelling</t>
   </si>
   <si>
-    <t xml:space="preserve">Swelling of face and hands</t>
+    <t>Swelling of face and hands</t>
   </si>
   <si>
     <t>breathlessness</t>
@@ -453,7 +465,7 @@
     <t>r_danger_sign_present</t>
   </si>
   <si>
-    <t xml:space="preserve">if((selected(../vaginal_bleeding, 'yes')
+    <t>if((selected(../vaginal_bleeding, 'yes')
 or selected(../fits, 'yes')
 or selected(../severe_abdominal_pain, 'yes')
 or selected(../severe_headache, 'yes')
@@ -470,7 +482,7 @@
     <t>custom_translations</t>
   </si>
   <si>
-    <t xml:space="preserve">select_one translate_woman_label</t>
+    <t>select_one translate_woman_label</t>
   </si>
   <si>
     <t>custom_woman_label_translator</t>
@@ -485,7 +497,7 @@
     <t>jr:choice-name(${custom_woman_label_translator},'${custom_woman_label_translator}')</t>
   </si>
   <si>
-    <t xml:space="preserve">select_one translate_woman_start_label</t>
+    <t>select_one translate_woman_start_label</t>
   </si>
   <si>
     <t>custom_woman_start_label_translator</t>
@@ -509,7 +521,7 @@
     <t>${visit_confirm}</t>
   </si>
   <si>
-    <t xml:space="preserve">Whether or not the woman was taken to the health facility as recommended.</t>
+    <t>Whether or not the woman was taken to the health facility as recommended.</t>
   </si>
   <si>
     <t>__still_experiencing_danger_sign</t>
@@ -518,7 +530,7 @@
     <t>${danger_sign_present}</t>
   </si>
   <si>
-    <t xml:space="preserve">Whether or not the woman is still experiencing any danger signs.</t>
+    <t>Whether or not the woman is still experiencing any danger signs.</t>
   </si>
   <si>
     <t>__vaginal_bleeding</t>
@@ -527,7 +539,7 @@
     <t>${vaginal_bleeding}</t>
   </si>
   <si>
-    <t xml:space="preserve">Whether or not the woman is experiencing vaginal bleeding.</t>
+    <t>Whether or not the woman is experiencing vaginal bleeding.</t>
   </si>
   <si>
     <t>__fits</t>
@@ -536,7 +548,7 @@
     <t>${fits}</t>
   </si>
   <si>
-    <t xml:space="preserve">Whether or not the woman is suffering from fits.</t>
+    <t>Whether or not the woman is suffering from fits.</t>
   </si>
   <si>
     <t>__severe_abdominal_pain</t>
@@ -545,7 +557,7 @@
     <t>${severe_abdominal_pain}</t>
   </si>
   <si>
-    <t xml:space="preserve">Whether or not the woman is suffering from abdominal pain.</t>
+    <t>Whether or not the woman is suffering from abdominal pain.</t>
   </si>
   <si>
     <t>__severe_headache</t>
@@ -554,7 +566,7 @@
     <t>${severe_headache}</t>
   </si>
   <si>
-    <t xml:space="preserve">Whether or not the woman is suffering from severe headaches.</t>
+    <t>Whether or not the woman is suffering from severe headaches.</t>
   </si>
   <si>
     <t>__very_pale</t>
@@ -563,7 +575,7 @@
     <t>${very_pale}</t>
   </si>
   <si>
-    <t xml:space="preserve">Whether or not the woman appears very pale.</t>
+    <t>Whether or not the woman appears very pale.</t>
   </si>
   <si>
     <t>__fever</t>
@@ -572,7 +584,7 @@
     <t>${fever}</t>
   </si>
   <si>
-    <t xml:space="preserve">Whether or not the woman has a fever.</t>
+    <t>Whether or not the woman has a fever.</t>
   </si>
   <si>
     <t>__reduced_or_no_fetal_movements</t>
@@ -581,7 +593,7 @@
     <t>${reduced_or_no_fetal_movements}</t>
   </si>
   <si>
-    <t xml:space="preserve">Whether or not the woman is experiencing reduced or no fetal movements.</t>
+    <t>Whether or not the woman is experiencing reduced or no fetal movements.</t>
   </si>
   <si>
     <t>__breaking_water</t>
@@ -590,7 +602,7 @@
     <t>${breaking_water}</t>
   </si>
   <si>
-    <t xml:space="preserve">Whether or not the woman's water has broken.</t>
+    <t>Whether or not the woman's water has broken.</t>
   </si>
   <si>
     <t>__easily_tired</t>
@@ -599,7 +611,7 @@
     <t>${easily_tired}</t>
   </si>
   <si>
-    <t xml:space="preserve">Whether or not the woman tires easily.</t>
+    <t>Whether or not the woman tires easily.</t>
   </si>
   <si>
     <t>__face_hand_swelling</t>
@@ -608,7 +620,7 @@
     <t>${face_hand_swelling}</t>
   </si>
   <si>
-    <t xml:space="preserve">Whether or not the woman is suffering from swelling in the face and hands.</t>
+    <t>Whether or not the woman is suffering from swelling in the face and hands.</t>
   </si>
   <si>
     <t>__breathlessness</t>
@@ -617,7 +629,7 @@
     <t>${breathlessness}</t>
   </si>
   <si>
-    <t xml:space="preserve">Whether or not the woman is suffering from breathlessness.</t>
+    <t>Whether or not the woman is suffering from breathlessness.</t>
   </si>
   <si>
     <t>__has_danger_sign</t>
@@ -626,7 +638,7 @@
     <t>${r_danger_sign_present}</t>
   </si>
   <si>
-    <t xml:space="preserve">Whether or not any danger signs are present.</t>
+    <t>Whether or not any danger signs are present.</t>
   </si>
   <si>
     <t>meta</t>
@@ -650,7 +662,7 @@
     <t>../../../inputs/contact/parent/_id</t>
   </si>
   <si>
-    <t xml:space="preserve">Household UUID</t>
+    <t>Household UUID</t>
   </si>
   <si>
     <t>__source</t>
@@ -695,7 +707,7 @@
     <t>woman</t>
   </si>
   <si>
-    <t xml:space="preserve">the woman</t>
+    <t>the woman</t>
   </si>
   <si>
     <t>translate_woman_start_label</t>
@@ -704,7 +716,7 @@
     <t>woman-start</t>
   </si>
   <si>
-    <t xml:space="preserve">The woman</t>
+    <t>The woman</t>
   </si>
   <si>
     <t>form_title</t>
@@ -728,7 +740,7 @@
     <t>default_language</t>
   </si>
   <si>
-    <t xml:space="preserve">Pregnancy danger sign follow-up</t>
+    <t>Pregnancy danger sign follow-up</t>
   </si>
   <si>
     <t>pregnancy_danger_sign_follow_up</t>
@@ -746,31 +758,31 @@
     <t>upto_2_months_ago</t>
   </si>
   <si>
-    <t xml:space="preserve">Upto 2 Months Ago</t>
+    <t>Upto 2 Months Ago</t>
   </si>
   <si>
     <t>upto_3_months_ago</t>
   </si>
   <si>
-    <t xml:space="preserve">Upto 3 Months Ago</t>
+    <t>Upto 3 Months Ago</t>
   </si>
   <si>
     <t>upto_4_months_ago</t>
   </si>
   <si>
-    <t xml:space="preserve">Upto 4 Months Ago</t>
+    <t>Upto 4 Months Ago</t>
   </si>
   <si>
     <t>between_5_and_6_months_ago</t>
   </si>
   <si>
-    <t xml:space="preserve">Between 5 And 6 Months Ago</t>
+    <t>Between 5 And 6 Months Ago</t>
   </si>
   <si>
     <t>between_7_and_8_months_ago</t>
   </si>
   <si>
-    <t xml:space="preserve">Between 7 And 8 Months Ago</t>
+    <t>Between 7 And 8 Months Ago</t>
   </si>
   <si>
     <t>trimester1_choices</t>
@@ -779,37 +791,37 @@
     <t>eat_extra_meal</t>
   </si>
   <si>
-    <t xml:space="preserve">Eat a balanced diet daily, and one extra meal and water to help the baby grow well and for you to remain strong and healthy</t>
+    <t>Eat a balanced diet daily, and one extra meal and water to help the baby grow well and for you to remain strong and healthy</t>
   </si>
   <si>
     <t>take_iron_and_folic_acid</t>
   </si>
   <si>
-    <t xml:space="preserve">Take iron and folic acid tablets</t>
+    <t>Take iron and folic acid tablets</t>
   </si>
   <si>
     <t>avoid_heavy_work</t>
   </si>
   <si>
-    <t xml:space="preserve">Avoid heavy work, rest more</t>
+    <t>Avoid heavy work, rest more</t>
   </si>
   <si>
     <t>sleep_under_bednet</t>
   </si>
   <si>
-    <t xml:space="preserve">Sleep under an insecticide treated bednet</t>
+    <t>Sleep under an insecticide treated bednet</t>
   </si>
   <si>
     <t>go_for_anc_visit</t>
   </si>
   <si>
-    <t xml:space="preserve">Go for an antenantal care visit as soon as you know you are pregnant, and at least four times during the pregnancy</t>
+    <t>Go for an antenantal care visit as soon as you know you are pregnant, and at least four times during the pregnancy</t>
   </si>
   <si>
     <t>develop_birth_plan</t>
   </si>
   <si>
-    <t xml:space="preserve">Develop a birth plan to ensure readiness for the arrival of the unborn baby</t>
+    <t>Develop a birth plan to ensure readiness for the arrival of the unborn baby</t>
   </si>
   <si>
     <t>trimester2_choices</t>
@@ -818,7 +830,7 @@
     <t>couselling_on_exclusive_breastfeeding</t>
   </si>
   <si>
-    <t xml:space="preserve">Give your baby breast milk only (exclusive breastfeeding) for the first six months and continue breastfeeding for the first two years for good health</t>
+    <t>Give your baby breast milk only (exclusive breastfeeding) for the first six months and continue breastfeeding for the first two years for good health</t>
   </si>
   <si>
     <t>conditions</t>
@@ -827,7 +839,7 @@
     <t>heart_condition</t>
   </si>
   <si>
-    <t xml:space="preserve">Heart condition</t>
+    <t>Heart condition</t>
   </si>
   <si>
     <t>asthma</t>
@@ -839,13 +851,13 @@
     <t>high_blood_pressure</t>
   </si>
   <si>
-    <t xml:space="preserve">High blood pressure</t>
+    <t>High blood pressure</t>
   </si>
   <si>
     <t>known_diabetes</t>
   </si>
   <si>
-    <t xml:space="preserve">Known diabetes</t>
+    <t>Known diabetes</t>
   </si>
   <si>
     <t>other</t>
@@ -866,19 +878,19 @@
     <t>fp_methods</t>
   </si>
   <si>
-    <t xml:space="preserve">Combined oral contraceptives</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Progesterone only pills</t>
+    <t>Combined oral contraceptives</t>
+  </si>
+  <si>
+    <t>Progesterone only pills</t>
   </si>
   <si>
     <t>Injectibles</t>
   </si>
   <si>
-    <t xml:space="preserve">Implants (1 rod)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Implants (2 rods)</t>
+    <t>Implants (1 rod)</t>
+  </si>
+  <si>
+    <t>Implants (2 rods)</t>
   </si>
   <si>
     <t>IUD</t>
@@ -887,19 +899,19 @@
     <t>Condoms</t>
   </si>
   <si>
-    <t xml:space="preserve">Tubal ligation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cycle beads</t>
+    <t>Tubal ligation</t>
+  </si>
+  <si>
+    <t>Cycle beads</t>
   </si>
   <si>
     <t>reasons_not_on_fp</t>
   </si>
   <si>
-    <t xml:space="preserve">Wants to get pregnant</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Did not want FP</t>
+    <t>Wants to get pregnant</t>
+  </si>
+  <si>
+    <t>Did not want FP</t>
   </si>
   <si>
     <t>follow_up_methods</t>
@@ -908,13 +920,13 @@
     <t>in_person</t>
   </si>
   <si>
-    <t xml:space="preserve">In person</t>
+    <t>In person</t>
   </si>
   <si>
     <t>by_phone</t>
   </si>
   <si>
-    <t xml:space="preserve">By phone</t>
+    <t>By phone</t>
   </si>
   <si>
     <t>reasons_for_missing_visit</t>
@@ -923,25 +935,25 @@
     <t>not_reminded</t>
   </si>
   <si>
-    <t xml:space="preserve">She was not reminded</t>
+    <t>She was not reminded</t>
   </si>
   <si>
     <t>travelled</t>
   </si>
   <si>
-    <t xml:space="preserve">She had travelled</t>
+    <t>She had travelled</t>
   </si>
   <si>
     <t>no_lab_results</t>
   </si>
   <si>
-    <t xml:space="preserve">No Lab results yet</t>
+    <t>No Lab results yet</t>
   </si>
   <si>
     <t>too_early</t>
   </si>
   <si>
-    <t xml:space="preserve">It is too early to start clinic</t>
+    <t>It is too early to start clinic</t>
   </si>
   <si>
     <t>relocated</t>
@@ -956,19 +968,19 @@
     <t>referred</t>
   </si>
   <si>
-    <t xml:space="preserve">Referred the mother</t>
+    <t>Referred the mother</t>
   </si>
   <si>
     <t>key_message</t>
   </si>
   <si>
-    <t xml:space="preserve">Provided key health message</t>
+    <t>Provided key health message</t>
   </si>
   <si>
     <t>accompany</t>
   </si>
   <si>
-    <t xml:space="preserve">Accompany the mother to facility</t>
+    <t>Accompany the mother to facility</t>
   </si>
   <si>
     <t>recent_foods</t>
@@ -977,31 +989,31 @@
     <t>carbohydrates</t>
   </si>
   <si>
-    <t xml:space="preserve">Energy giving foods: sweet potatoes, cassava, wheat, maize</t>
+    <t>Energy giving foods: sweet potatoes, cassava, wheat, maize</t>
   </si>
   <si>
     <t>protein</t>
   </si>
   <si>
-    <t xml:space="preserve">Body building foods: Milk, eggs, meat</t>
+    <t>Body building foods: Milk, eggs, meat</t>
   </si>
   <si>
     <t>vegetables</t>
   </si>
   <si>
-    <t xml:space="preserve">Vegetables: Sukuma wiki, cabbages, traditional greens</t>
+    <t>Vegetables: Sukuma wiki, cabbages, traditional greens</t>
   </si>
   <si>
     <t>fruits</t>
   </si>
   <si>
-    <t xml:space="preserve">Fruits: Mangoes, ripe bananas, oranges</t>
+    <t>Fruits: Mangoes, ripe bananas, oranges</t>
   </si>
   <si>
     <t>none</t>
   </si>
   <si>
-    <t xml:space="preserve">None of the above</t>
+    <t>None of the above</t>
   </si>
   <si>
     <t>pos_neg</t>
@@ -1028,41 +1040,63 @@
     <t>feels_sick_when_using_it</t>
   </si>
   <si>
-    <t xml:space="preserve">Feels sick when using it</t>
+    <t>Feels sick when using it</t>
+  </si>
+  <si>
+    <t>string</t>
+  </si>
+  <si>
+    <t>select-contact type-person</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="160" formatCode="dd-MM-yyyy HH-mm-ss"/>
+    <numFmt numFmtId="164" formatCode="dd\-mm\-yyyy\ hh\-mm\-ss"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="9">
     <font>
+      <sz val="10"/>
+      <color theme="1"/>
       <name val="Arial"/>
-      <color theme="1"/>
-      <sz val="10.000000"/>
     </font>
     <font>
       <b/>
-    </font>
-    <font/>
-    <font>
+      <sz val="10"/>
       <name val="Arial"/>
     </font>
     <font>
+      <sz val="10"/>
       <name val="Arial"/>
-      <b/>
     </font>
     <font>
-      <name val="Calibri"/>
-      <b/>
-      <sz val="11.000000"/>
+      <sz val="10"/>
+      <name val="Arial"/>
     </font>
     <font>
+      <b/>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <name val="Calibri"/>
-      <sz val="11.000000"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <name val="Tahoma"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="Tahoma"/>
     </font>
   </fonts>
   <fills count="16">
@@ -1153,7 +1187,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor indexed="65"/>
-        <bgColor indexed="65"/>
       </patternFill>
     </fill>
   </fills>
@@ -1167,70 +1200,70 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="31">
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
-    <xf fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf fontId="2" fillId="2" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf fontId="2" fillId="3" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf fontId="2" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf fontId="2" fillId="4" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf fontId="2" fillId="5" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf fontId="2" fillId="6" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf fontId="2" fillId="7" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf fontId="2" fillId="7" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf fontId="2" fillId="8" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf fontId="2" fillId="9" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf fontId="3" fillId="9" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf fontId="3" fillId="8" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf fontId="3" fillId="9" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf fontId="4" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf fontId="5" fillId="10" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf fontId="5" fillId="11" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf fontId="5" fillId="12" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf fontId="5" fillId="13" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf fontId="5" fillId="14" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf fontId="5" fillId="9" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf fontId="5" fillId="7" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf fontId="3" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf fontId="3" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf fontId="2" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf fontId="5" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf fontId="2" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf fontId="3" fillId="0" borderId="0" numFmtId="160" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf fontId="6" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf fontId="3" fillId="15" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -1243,6 +1276,9 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
   </extLst>
 </styleSheet>
 </file>
@@ -1253,291 +1289,8 @@
 </personList>
 </file>
 
-<file path=xl/theme/theme.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
-  <a:themeElements>
-    <a:clrScheme name="Office">
-      <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
-      </a:dk1>
-      <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
-      </a:lt1>
-      <a:dk2>
-        <a:srgbClr val="1F497D"/>
-      </a:dk2>
-      <a:lt2>
-        <a:srgbClr val="EEECE1"/>
-      </a:lt2>
-      <a:accent1>
-        <a:srgbClr val="4F81BD"/>
-      </a:accent1>
-      <a:accent2>
-        <a:srgbClr val="C0504D"/>
-      </a:accent2>
-      <a:accent3>
-        <a:srgbClr val="9BBB59"/>
-      </a:accent3>
-      <a:accent4>
-        <a:srgbClr val="8064A2"/>
-      </a:accent4>
-      <a:accent5>
-        <a:srgbClr val="4BACC6"/>
-      </a:accent5>
-      <a:accent6>
-        <a:srgbClr val="F79646"/>
-      </a:accent6>
-      <a:hlink>
-        <a:srgbClr val="0000FF"/>
-      </a:hlink>
-      <a:folHlink>
-        <a:srgbClr val="800080"/>
-      </a:folHlink>
-    </a:clrScheme>
-    <a:fontScheme name="Office">
-      <a:majorFont>
-        <a:latin typeface="Cambria"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ ゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Angsana New"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-      </a:majorFont>
-      <a:minorFont>
-        <a:latin typeface="Calibri"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ 明朝"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Cordia New"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-      </a:minorFont>
-    </a:fontScheme>
-    <a:fmtScheme name="Office">
-      <a:fillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="35000">
-              <a:schemeClr val="phClr">
-                <a:tint val="37000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:tint val="15000"/>
-                <a:satMod val="350000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
-                <a:satMod val="130000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="80000">
-              <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
-                <a:satMod val="130000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
-                <a:satMod val="135000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="16200000" scaled="0"/>
-        </a:gradFill>
-      </a:fillStyleLst>
-      <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr">
-              <a:shade val="95000"/>
-              <a:satMod val="105000"/>
-            </a:schemeClr>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </a:lnStyleLst>
-      <a:effectStyleLst>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="38000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-          <a:scene3d>
-            <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
-            </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
-            </a:lightRig>
-          </a:scene3d>
-          <a:sp3d>
-            <a:bevelT w="63500" h="25400"/>
-          </a:sp3d>
-        </a:effectStyle>
-      </a:effectStyleLst>
-      <a:bgFillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="40000"/>
-                <a:satMod val="350000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="40000">
-              <a:schemeClr val="phClr">
-                <a:tint val="45000"/>
-                <a:shade val="99000"/>
-                <a:satMod val="350000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="20000"/>
-                <a:satMod val="255000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
-          </a:path>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="80000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="30000"/>
-                <a:satMod val="200000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
-          </a:path>
-        </a:gradFill>
-      </a:bgFillStyleLst>
-    </a:fmtScheme>
-  </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
-</a:theme>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:p="http://schemas.openxmlformats.org/presentationml/2006/main" name="">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <a:themeElements>
     <a:clrScheme name="">
       <a:dk1>
@@ -1589,7 +1342,7 @@
         <a:cs typeface="Arial"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="">
+    <a:fmtScheme>
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1660,6 +1413,7 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
@@ -1675,35 +1429,35 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
-    <outlinePr applyStyles="0" summaryBelow="0" summaryRight="0" showOutlineSymbols="1"/>
-    <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr defaultColWidth="14.43" defaultRowHeight="15" customHeight="1"/>
+  <dimension ref="A1:AJ97"/>
+  <sheetFormatPr defaultColWidth="14.44140625" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="19"/>
-    <col customWidth="1" min="2" max="2" width="34.289999999999999"/>
-    <col customWidth="1" min="3" max="3" width="43.289999999999999"/>
-    <col customWidth="1" hidden="1" min="4" max="5" width="8.5700000000000003"/>
-    <col customWidth="1" hidden="1" min="6" max="6" width="8.7100000000000009"/>
-    <col customWidth="1" hidden="1" min="7" max="7" width="8.8599999999999994"/>
-    <col customWidth="1" hidden="1" min="8" max="9" width="8.1400000000000006"/>
-    <col customWidth="1" min="10" max="10" width="14.43"/>
-    <col customWidth="1" min="11" max="11" width="53.859999999999999"/>
-    <col customWidth="1" min="12" max="12" width="17.43"/>
-    <col customWidth="1" min="13" max="13" width="37.710000000000001"/>
-    <col customWidth="1" min="14" max="14" width="32.710000000000001"/>
-    <col customWidth="1" hidden="1" min="15" max="20" width="25.859999999999999"/>
-    <col customWidth="1" min="21" max="21" width="73.859999999999999"/>
-    <col customWidth="1" min="22" max="22" width="14.43"/>
-    <col customWidth="1" min="23" max="23" width="30"/>
-    <col customWidth="1" hidden="1" min="24" max="29" width="14.43"/>
-    <col customWidth="1" min="30" max="30" width="14.43"/>
-    <col customWidth="1" min="31" max="36" width="29.859999999999999"/>
+    <col min="1" max="1" width="19" customWidth="1"/>
+    <col min="2" max="2" width="34.33203125" customWidth="1"/>
+    <col min="3" max="3" width="43.33203125" customWidth="1"/>
+    <col min="4" max="5" width="8.5546875" hidden="1" customWidth="1"/>
+    <col min="6" max="6" width="8.6640625" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="8.88671875" hidden="1" customWidth="1"/>
+    <col min="8" max="9" width="8.109375" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="14.44140625" customWidth="1"/>
+    <col min="11" max="11" width="53.88671875" customWidth="1"/>
+    <col min="12" max="12" width="22" customWidth="1"/>
+    <col min="13" max="13" width="37.6640625" customWidth="1"/>
+    <col min="14" max="14" width="32.6640625" customWidth="1"/>
+    <col min="15" max="20" width="25.88671875" hidden="1" customWidth="1"/>
+    <col min="21" max="21" width="73.88671875" customWidth="1"/>
+    <col min="22" max="22" width="14.44140625" customWidth="1"/>
+    <col min="23" max="23" width="30" customWidth="1"/>
+    <col min="24" max="29" width="14.44140625" hidden="1" customWidth="1"/>
+    <col min="30" max="30" width="14.44140625" customWidth="1"/>
+    <col min="31" max="36" width="29.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.75" customHeight="1">
+    <row r="1" spans="1:36" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1809,7 +1563,7 @@
       <c r="AI1" s="1"/>
       <c r="AJ1" s="1"/>
     </row>
-    <row r="2" ht="15.75" customHeight="1">
+    <row r="2" spans="1:36" ht="15.75" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>34</v>
       </c>
@@ -1857,7 +1611,7 @@
       <c r="AI2" s="3"/>
       <c r="AJ2" s="3"/>
     </row>
-    <row r="3" ht="15.75" customHeight="1">
+    <row r="3" spans="1:36" ht="15.75" customHeight="1">
       <c r="A3" s="2" t="s">
         <v>39</v>
       </c>
@@ -1903,7 +1657,7 @@
       <c r="AI3" s="3"/>
       <c r="AJ3" s="3"/>
     </row>
-    <row r="4" ht="15.75" customHeight="1">
+    <row r="4" spans="1:36" ht="15.75" customHeight="1">
       <c r="A4" s="2" t="s">
         <v>39</v>
       </c>
@@ -1947,7 +1701,7 @@
       <c r="AI4" s="3"/>
       <c r="AJ4" s="3"/>
     </row>
-    <row r="5" ht="15.75" customHeight="1">
+    <row r="5" spans="1:36" ht="15.75" customHeight="1">
       <c r="A5" s="2" t="s">
         <v>34</v>
       </c>
@@ -1991,15 +1745,15 @@
       <c r="AI5" s="3"/>
       <c r="AJ5" s="3"/>
     </row>
-    <row r="6" ht="15.75" customHeight="1">
+    <row r="6" spans="1:36" ht="15.75" customHeight="1">
       <c r="A6" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="C6" s="3" t="s">
         <v>47</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>48</v>
       </c>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
@@ -2010,7 +1764,7 @@
       <c r="J6" s="3"/>
       <c r="K6" s="3"/>
       <c r="L6" s="3" t="s">
-        <v>49</v>
+        <v>322</v>
       </c>
       <c r="M6" s="3"/>
       <c r="N6" s="3"/>
@@ -2037,7 +1791,7 @@
       <c r="AI6" s="3"/>
       <c r="AJ6" s="3"/>
     </row>
-    <row r="7" ht="15.75" customHeight="1">
+    <row r="7" spans="1:36" ht="15.75" customHeight="1">
       <c r="A7" s="2" t="s">
         <v>39</v>
       </c>
@@ -2045,7 +1799,7 @@
         <v>1</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
@@ -2081,15 +1835,15 @@
       <c r="AI7" s="3"/>
       <c r="AJ7" s="3"/>
     </row>
-    <row r="8" ht="15.75" customHeight="1">
+    <row r="8" spans="1:36" ht="15.75" customHeight="1">
       <c r="A8" s="2" t="s">
         <v>39</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
@@ -2125,15 +1879,15 @@
       <c r="AI8" s="3"/>
       <c r="AJ8" s="3"/>
     </row>
-    <row r="9" ht="15.75" customHeight="1">
+    <row r="9" spans="1:36" ht="15.75" customHeight="1">
       <c r="A9" s="2" t="s">
         <v>39</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
@@ -2169,15 +1923,15 @@
       <c r="AI9" s="3"/>
       <c r="AJ9" s="3"/>
     </row>
-    <row r="10" ht="15.75" customHeight="1">
+    <row r="10" spans="1:36" ht="15.75" customHeight="1">
       <c r="A10" s="2" t="s">
         <v>39</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D10" s="3"/>
       <c r="E10" s="3"/>
@@ -2215,15 +1969,15 @@
       <c r="AI10" s="3"/>
       <c r="AJ10" s="3"/>
     </row>
-    <row r="11" ht="15.75" customHeight="1">
+    <row r="11" spans="1:36" ht="15.75" customHeight="1">
       <c r="A11" s="2" t="s">
         <v>39</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D11" s="3"/>
       <c r="E11" s="3"/>
@@ -2259,12 +2013,12 @@
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
     </row>
-    <row r="12" ht="15.75" customHeight="1">
+    <row r="12" spans="1:36" ht="15.75" customHeight="1">
       <c r="A12" s="2" t="s">
         <v>34</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>36</v>
@@ -2303,15 +2057,15 @@
       <c r="AI12" s="3"/>
       <c r="AJ12" s="3"/>
     </row>
-    <row r="13" ht="15.75" customHeight="1">
+    <row r="13" spans="1:36" ht="15.75" customHeight="1">
       <c r="A13" s="2" t="s">
         <v>39</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D13" s="3"/>
       <c r="E13" s="3"/>
@@ -2347,12 +2101,12 @@
       <c r="AI13" s="3"/>
       <c r="AJ13" s="3"/>
     </row>
-    <row r="14" ht="15.75" customHeight="1">
+    <row r="14" spans="1:36" ht="15.75" customHeight="1">
       <c r="A14" s="2" t="s">
         <v>34</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>36</v>
@@ -2391,7 +2145,7 @@
       <c r="AI14" s="3"/>
       <c r="AJ14" s="3"/>
     </row>
-    <row r="15" ht="15.75" customHeight="1">
+    <row r="15" spans="1:36" ht="15.75" customHeight="1">
       <c r="A15" s="2" t="s">
         <v>34</v>
       </c>
@@ -2435,15 +2189,15 @@
       <c r="AI15" s="3"/>
       <c r="AJ15" s="3"/>
     </row>
-    <row r="16" ht="15.75" customHeight="1">
+    <row r="16" spans="1:36" ht="15.75" customHeight="1">
       <c r="A16" s="2" t="s">
         <v>39</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
@@ -2479,15 +2233,15 @@
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
     </row>
-    <row r="17" ht="15.75" customHeight="1">
+    <row r="17" spans="1:36" ht="15.75" customHeight="1">
       <c r="A17" s="2" t="s">
         <v>39</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D17" s="3"/>
       <c r="E17" s="3"/>
@@ -2523,9 +2277,9 @@
       <c r="AI17" s="3"/>
       <c r="AJ17" s="3"/>
     </row>
-    <row r="18" ht="15.75" customHeight="1">
+    <row r="18" spans="1:36" ht="15.75" customHeight="1">
       <c r="A18" s="2" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>45</v>
@@ -2565,12 +2319,12 @@
       <c r="AI18" s="3"/>
       <c r="AJ18" s="3"/>
     </row>
-    <row r="19" ht="15.75" customHeight="1">
+    <row r="19" spans="1:36" ht="15.75" customHeight="1">
       <c r="A19" s="2" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C19" s="3"/>
       <c r="D19" s="3"/>
@@ -2607,12 +2361,12 @@
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
     </row>
-    <row r="20" ht="15.75" customHeight="1">
+    <row r="20" spans="1:36" ht="15.75" customHeight="1">
       <c r="A20" s="2" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C20" s="3"/>
       <c r="D20" s="3"/>
@@ -2649,9 +2403,9 @@
       <c r="AI20" s="3"/>
       <c r="AJ20" s="3"/>
     </row>
-    <row r="21" ht="15.75" customHeight="1">
+    <row r="21" spans="1:36" ht="15.75" customHeight="1">
       <c r="A21" s="2" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>45</v>
@@ -2691,9 +2445,9 @@
       <c r="AI21" s="3"/>
       <c r="AJ21" s="3"/>
     </row>
-    <row r="22" ht="15.75" customHeight="1">
+    <row r="22" spans="1:36" ht="15.75" customHeight="1">
       <c r="A22" s="2" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>35</v>
@@ -2733,15 +2487,15 @@
       <c r="AI22" s="3"/>
       <c r="AJ22" s="3"/>
     </row>
-    <row r="23" ht="15.75" customHeight="1">
+    <row r="23" spans="1:36" ht="15.75" customHeight="1">
       <c r="AF23" s="4"/>
     </row>
-    <row r="24" ht="15.75" customHeight="1">
+    <row r="24" spans="1:36" ht="15.75" customHeight="1">
       <c r="A24" s="5" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C24" s="6" t="s">
         <v>36</v>
@@ -2764,7 +2518,7 @@
       <c r="S24" s="6"/>
       <c r="T24" s="6"/>
       <c r="U24" s="6" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="V24" s="6"/>
       <c r="W24" s="6"/>
@@ -2781,17 +2535,17 @@
       </c>
       <c r="AG24" s="6"/>
       <c r="AH24" s="6" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="AI24" s="6"/>
       <c r="AJ24" s="6"/>
     </row>
-    <row r="25" ht="15.75" customHeight="1">
+    <row r="25" spans="1:36" ht="15.75" customHeight="1">
       <c r="A25" s="5" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C25" s="6" t="s">
         <v>36</v>
@@ -2814,7 +2568,7 @@
       <c r="S25" s="6"/>
       <c r="T25" s="6"/>
       <c r="U25" s="6" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="V25" s="6"/>
       <c r="W25" s="6"/>
@@ -2831,17 +2585,17 @@
       </c>
       <c r="AG25" s="6"/>
       <c r="AH25" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="AI25" s="6"/>
       <c r="AJ25" s="6"/>
     </row>
-    <row r="26" ht="15.75" customHeight="1">
+    <row r="26" spans="1:36" ht="15.75" customHeight="1">
       <c r="A26" s="5" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C26" s="6" t="s">
         <v>36</v>
@@ -2864,7 +2618,7 @@
       <c r="S26" s="6"/>
       <c r="T26" s="6"/>
       <c r="U26" s="6" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="V26" s="6"/>
       <c r="W26" s="6"/>
@@ -2881,17 +2635,17 @@
       </c>
       <c r="AG26" s="6"/>
       <c r="AH26" s="6" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="AI26" s="6"/>
       <c r="AJ26" s="6"/>
     </row>
-    <row r="27" ht="15.75" customHeight="1">
+    <row r="27" spans="1:36" ht="15.75" customHeight="1">
       <c r="A27" s="5" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C27" s="6" t="s">
         <v>36</v>
@@ -2914,7 +2668,7 @@
       <c r="S27" s="6"/>
       <c r="T27" s="6"/>
       <c r="U27" s="6" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="V27" s="6"/>
       <c r="W27" s="6"/>
@@ -2931,17 +2685,17 @@
       </c>
       <c r="AG27" s="6"/>
       <c r="AH27" s="6" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="AI27" s="6"/>
       <c r="AJ27" s="6"/>
     </row>
-    <row r="28" ht="15.75" customHeight="1">
+    <row r="28" spans="1:36" ht="15.75" customHeight="1">
       <c r="A28" s="5" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C28" s="6" t="s">
         <v>36</v>
@@ -2964,7 +2718,7 @@
       <c r="S28" s="6"/>
       <c r="T28" s="6"/>
       <c r="U28" s="6" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="V28" s="6"/>
       <c r="W28" s="6"/>
@@ -2981,17 +2735,17 @@
       </c>
       <c r="AG28" s="6"/>
       <c r="AH28" s="6" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="AI28" s="6"/>
       <c r="AJ28" s="6"/>
     </row>
-    <row r="29" ht="15.75" customHeight="1">
+    <row r="29" spans="1:36" ht="15.75" customHeight="1">
       <c r="A29" s="5" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C29" s="6" t="s">
         <v>36</v>
@@ -3014,7 +2768,7 @@
       <c r="S29" s="6"/>
       <c r="T29" s="6"/>
       <c r="U29" s="6" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="V29" s="6"/>
       <c r="W29" s="6"/>
@@ -3031,17 +2785,17 @@
       </c>
       <c r="AG29" s="6"/>
       <c r="AH29" s="6" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="AI29" s="6"/>
       <c r="AJ29" s="6"/>
     </row>
-    <row r="30" ht="15.75" customHeight="1">
+    <row r="30" spans="1:36" ht="15.75" customHeight="1">
       <c r="A30" s="5" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C30" s="6" t="s">
         <v>36</v>
@@ -3064,7 +2818,7 @@
       <c r="S30" s="6"/>
       <c r="T30" s="6"/>
       <c r="U30" s="6" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="V30" s="6"/>
       <c r="W30" s="6"/>
@@ -3081,17 +2835,17 @@
       </c>
       <c r="AG30" s="6"/>
       <c r="AH30" s="6" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="AI30" s="6"/>
       <c r="AJ30" s="6"/>
     </row>
-    <row r="31" ht="15.75" customHeight="1">
+    <row r="31" spans="1:36" ht="15.75" customHeight="1">
       <c r="A31" s="5" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C31" s="6" t="s">
         <v>36</v>
@@ -3114,7 +2868,7 @@
       <c r="S31" s="6"/>
       <c r="T31" s="6"/>
       <c r="U31" s="6" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="V31" s="6"/>
       <c r="W31" s="6"/>
@@ -3131,17 +2885,17 @@
       </c>
       <c r="AG31" s="6"/>
       <c r="AH31" s="6" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="AI31" s="6"/>
       <c r="AJ31" s="6"/>
     </row>
-    <row r="32" ht="15.75" customHeight="1">
+    <row r="32" spans="1:36" ht="15.75" customHeight="1">
       <c r="A32" s="5" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C32" s="6" t="s">
         <v>36</v>
@@ -3164,7 +2918,7 @@
       <c r="S32" s="6"/>
       <c r="T32" s="6"/>
       <c r="U32" s="6" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="V32" s="6"/>
       <c r="W32" s="6"/>
@@ -3179,27 +2933,27 @@
       <c r="AF32" s="6"/>
       <c r="AG32" s="6"/>
       <c r="AH32" s="6" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="AI32" s="6"/>
       <c r="AJ32" s="6"/>
     </row>
-    <row r="33" ht="15.75" customHeight="1">
+    <row r="33" spans="1:36" ht="15.75" customHeight="1">
       <c r="A33" s="4"/>
       <c r="B33" s="4"/>
       <c r="C33" s="4"/>
       <c r="K33" s="4"/>
       <c r="L33" s="4"/>
     </row>
-    <row r="34" ht="15.75" customHeight="1">
+    <row r="34" spans="1:36" ht="15.75" customHeight="1">
       <c r="A34" s="7" t="s">
         <v>34</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C34" s="8" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D34" s="8"/>
       <c r="E34" s="8"/>
@@ -3237,15 +2991,15 @@
       <c r="AI34" s="8"/>
       <c r="AJ34" s="8"/>
     </row>
-    <row r="35" ht="15.75" customHeight="1">
+    <row r="35" spans="1:36" ht="15.75" customHeight="1">
       <c r="A35" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="B35" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="C35" s="8" t="s">
         <v>94</v>
-      </c>
-      <c r="B35" s="7" t="s">
-        <v>95</v>
-      </c>
-      <c r="C35" s="8" t="s">
-        <v>96</v>
       </c>
       <c r="D35" s="8"/>
       <c r="E35" s="8"/>
@@ -3254,7 +3008,7 @@
       <c r="H35" s="8"/>
       <c r="I35" s="8"/>
       <c r="J35" s="8" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="K35" s="8"/>
       <c r="L35" s="8"/>
@@ -3283,15 +3037,15 @@
       <c r="AI35" s="8"/>
       <c r="AJ35" s="8"/>
     </row>
-    <row r="36" ht="15.75" customHeight="1">
+    <row r="36" spans="1:36" ht="15.75" customHeight="1">
       <c r="A36" s="7" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B36" s="7" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C36" s="8" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D36" s="8"/>
       <c r="E36" s="8"/>
@@ -3300,7 +3054,7 @@
       <c r="H36" s="8"/>
       <c r="I36" s="8"/>
       <c r="J36" s="8" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="K36" s="8"/>
       <c r="L36" s="8"/>
@@ -3329,15 +3083,15 @@
       <c r="AI36" s="8"/>
       <c r="AJ36" s="8"/>
     </row>
-    <row r="37" ht="15.75" customHeight="1">
+    <row r="37" spans="1:36" ht="15.75" customHeight="1">
       <c r="A37" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="B37" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="C37" s="8" t="s">
         <v>100</v>
-      </c>
-      <c r="B37" s="7" t="s">
-        <v>101</v>
-      </c>
-      <c r="C37" s="8" t="s">
-        <v>102</v>
       </c>
       <c r="D37" s="8"/>
       <c r="E37" s="8"/>
@@ -3347,7 +3101,7 @@
       <c r="I37" s="8"/>
       <c r="J37" s="8"/>
       <c r="K37" s="8" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="L37" s="8"/>
       <c r="M37" s="8"/>
@@ -3377,15 +3131,15 @@
       <c r="AI37" s="8"/>
       <c r="AJ37" s="8"/>
     </row>
-    <row r="38" ht="15.75" customHeight="1">
+    <row r="38" spans="1:36" ht="15.75" customHeight="1">
       <c r="A38" s="7" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B38" s="7" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C38" s="8" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="D38" s="8"/>
       <c r="E38" s="8"/>
@@ -3395,7 +3149,7 @@
       <c r="I38" s="8"/>
       <c r="J38" s="8"/>
       <c r="K38" s="8" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="L38" s="8"/>
       <c r="M38" s="8"/>
@@ -3425,15 +3179,15 @@
       <c r="AI38" s="8"/>
       <c r="AJ38" s="8"/>
     </row>
-    <row r="39" ht="15.75" customHeight="1">
+    <row r="39" spans="1:36" ht="15.75" customHeight="1">
       <c r="A39" s="7" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B39" s="7" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C39" s="8" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D39" s="8"/>
       <c r="E39" s="8"/>
@@ -3443,7 +3197,7 @@
       <c r="I39" s="8"/>
       <c r="J39" s="8"/>
       <c r="K39" s="8" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="L39" s="8"/>
       <c r="M39" s="8"/>
@@ -3473,15 +3227,15 @@
       <c r="AI39" s="8"/>
       <c r="AJ39" s="8"/>
     </row>
-    <row r="40" ht="15.75" customHeight="1">
+    <row r="40" spans="1:36" ht="15.75" customHeight="1">
       <c r="A40" s="7" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B40" s="7" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C40" s="8" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="D40" s="8"/>
       <c r="E40" s="8"/>
@@ -3491,7 +3245,7 @@
       <c r="I40" s="8"/>
       <c r="J40" s="8"/>
       <c r="K40" s="8" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="L40" s="8"/>
       <c r="M40" s="8"/>
@@ -3521,15 +3275,15 @@
       <c r="AI40" s="8"/>
       <c r="AJ40" s="8"/>
     </row>
-    <row r="41" ht="15.75" customHeight="1">
+    <row r="41" spans="1:36" ht="15.75" customHeight="1">
       <c r="A41" s="7" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B41" s="7" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C41" s="8" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D41" s="8"/>
       <c r="E41" s="8"/>
@@ -3538,10 +3292,10 @@
       <c r="H41" s="8"/>
       <c r="I41" s="8"/>
       <c r="J41" s="8" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="K41" s="8" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="L41" s="8"/>
       <c r="M41" s="8"/>
@@ -3569,15 +3323,15 @@
       <c r="AI41" s="8"/>
       <c r="AJ41" s="8"/>
     </row>
-    <row r="42" ht="15.75" customHeight="1">
+    <row r="42" spans="1:36" ht="15.75" customHeight="1">
       <c r="A42" s="7" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B42" s="7" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C42" s="8" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D42" s="8"/>
       <c r="E42" s="8"/>
@@ -3586,10 +3340,10 @@
       <c r="H42" s="8"/>
       <c r="I42" s="8"/>
       <c r="J42" s="8" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="K42" s="8" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="L42" s="8"/>
       <c r="M42" s="8"/>
@@ -3617,15 +3371,15 @@
       <c r="AI42" s="8"/>
       <c r="AJ42" s="8"/>
     </row>
-    <row r="43" ht="15.75" customHeight="1">
+    <row r="43" spans="1:36" ht="15.75" customHeight="1">
       <c r="A43" s="7" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B43" s="7" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C43" s="8" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D43" s="8"/>
       <c r="E43" s="8"/>
@@ -3634,10 +3388,10 @@
       <c r="H43" s="8"/>
       <c r="I43" s="8"/>
       <c r="J43" s="8" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="K43" s="8" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="L43" s="8"/>
       <c r="M43" s="8"/>
@@ -3665,15 +3419,15 @@
       <c r="AI43" s="8"/>
       <c r="AJ43" s="8"/>
     </row>
-    <row r="44" ht="15.75" customHeight="1">
+    <row r="44" spans="1:36" ht="15.75" customHeight="1">
       <c r="A44" s="7" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B44" s="7" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C44" s="8" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D44" s="8"/>
       <c r="E44" s="8"/>
@@ -3682,10 +3436,10 @@
       <c r="H44" s="8"/>
       <c r="I44" s="8"/>
       <c r="J44" s="8" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="K44" s="8" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="L44" s="8"/>
       <c r="M44" s="8"/>
@@ -3713,15 +3467,15 @@
       <c r="AI44" s="8"/>
       <c r="AJ44" s="8"/>
     </row>
-    <row r="45" ht="15.75" customHeight="1">
+    <row r="45" spans="1:36" ht="15.75" customHeight="1">
       <c r="A45" s="7" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B45" s="7" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C45" s="8" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="D45" s="8"/>
       <c r="E45" s="8"/>
@@ -3730,10 +3484,10 @@
       <c r="H45" s="8"/>
       <c r="I45" s="8"/>
       <c r="J45" s="8" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="K45" s="8" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="L45" s="8"/>
       <c r="M45" s="8"/>
@@ -3761,15 +3515,15 @@
       <c r="AI45" s="8"/>
       <c r="AJ45" s="8"/>
     </row>
-    <row r="46" ht="15.75" customHeight="1">
+    <row r="46" spans="1:36" ht="15.75" customHeight="1">
       <c r="A46" s="7" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B46" s="7" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C46" s="8" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D46" s="8"/>
       <c r="E46" s="8"/>
@@ -3778,10 +3532,10 @@
       <c r="H46" s="8"/>
       <c r="I46" s="8"/>
       <c r="J46" s="8" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="K46" s="8" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="L46" s="8"/>
       <c r="M46" s="8"/>
@@ -3809,15 +3563,15 @@
       <c r="AI46" s="8"/>
       <c r="AJ46" s="8"/>
     </row>
-    <row r="47" ht="15.75" customHeight="1">
+    <row r="47" spans="1:36" ht="15.75" customHeight="1">
       <c r="A47" s="7" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B47" s="7" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C47" s="8" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="D47" s="8"/>
       <c r="E47" s="8"/>
@@ -3826,10 +3580,10 @@
       <c r="H47" s="8"/>
       <c r="I47" s="8"/>
       <c r="J47" s="8" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="K47" s="8" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="L47" s="8"/>
       <c r="M47" s="8"/>
@@ -3857,15 +3611,15 @@
       <c r="AI47" s="8"/>
       <c r="AJ47" s="8"/>
     </row>
-    <row r="48" ht="15.75" customHeight="1">
+    <row r="48" spans="1:36" ht="15.75" customHeight="1">
       <c r="A48" s="7" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B48" s="7" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C48" s="8" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D48" s="8"/>
       <c r="E48" s="8"/>
@@ -3874,10 +3628,10 @@
       <c r="H48" s="8"/>
       <c r="I48" s="8"/>
       <c r="J48" s="8" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="K48" s="8" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="L48" s="8"/>
       <c r="M48" s="8"/>
@@ -3905,15 +3659,15 @@
       <c r="AI48" s="8"/>
       <c r="AJ48" s="8"/>
     </row>
-    <row r="49" ht="15.75" customHeight="1">
+    <row r="49" spans="1:36" ht="15.75" customHeight="1">
       <c r="A49" s="7" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B49" s="7" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C49" s="8" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="D49" s="8"/>
       <c r="E49" s="8"/>
@@ -3922,10 +3676,10 @@
       <c r="H49" s="8"/>
       <c r="I49" s="8"/>
       <c r="J49" s="8" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="K49" s="8" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="L49" s="8"/>
       <c r="M49" s="8"/>
@@ -3953,15 +3707,15 @@
       <c r="AI49" s="8"/>
       <c r="AJ49" s="8"/>
     </row>
-    <row r="50" ht="15.75" customHeight="1">
+    <row r="50" spans="1:36" ht="15.75" customHeight="1">
       <c r="A50" s="7" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B50" s="7" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C50" s="8" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="D50" s="8"/>
       <c r="E50" s="8"/>
@@ -3970,10 +3724,10 @@
       <c r="H50" s="8"/>
       <c r="I50" s="8"/>
       <c r="J50" s="8" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="K50" s="8" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="L50" s="8"/>
       <c r="M50" s="8"/>
@@ -4001,15 +3755,15 @@
       <c r="AI50" s="8"/>
       <c r="AJ50" s="8"/>
     </row>
-    <row r="51" ht="15.75" customHeight="1">
+    <row r="51" spans="1:36" ht="15.75" customHeight="1">
       <c r="A51" s="7" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B51" s="7" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C51" s="8" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D51" s="8"/>
       <c r="E51" s="8"/>
@@ -4018,10 +3772,10 @@
       <c r="H51" s="8"/>
       <c r="I51" s="8"/>
       <c r="J51" s="8" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="K51" s="8" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="L51" s="8"/>
       <c r="M51" s="8"/>
@@ -4049,12 +3803,12 @@
       <c r="AI51" s="8"/>
       <c r="AJ51" s="8"/>
     </row>
-    <row r="52" ht="15.75" customHeight="1">
+    <row r="52" spans="1:36" ht="15.75" customHeight="1">
       <c r="A52" s="7" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B52" s="7" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C52" s="8" t="s">
         <v>36</v>
@@ -4077,7 +3831,7 @@
       <c r="S52" s="8"/>
       <c r="T52" s="8"/>
       <c r="U52" s="9" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="V52" s="8"/>
       <c r="W52" s="8"/>
@@ -4097,12 +3851,12 @@
       <c r="AI52" s="8"/>
       <c r="AJ52" s="8"/>
     </row>
-    <row r="53" ht="15.75" customHeight="1">
+    <row r="53" spans="1:36" ht="15.75" customHeight="1">
       <c r="A53" s="7" t="s">
         <v>34</v>
       </c>
       <c r="B53" s="7" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C53" s="8" t="s">
         <v>36</v>
@@ -4145,12 +3899,12 @@
       <c r="AI53" s="8"/>
       <c r="AJ53" s="8"/>
     </row>
-    <row r="54" ht="15.75" customHeight="1">
+    <row r="54" spans="1:36" ht="15.75" customHeight="1">
       <c r="A54" s="7" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B54" s="7" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C54" s="8" t="s">
         <v>36</v>
@@ -4173,7 +3927,7 @@
       <c r="S54" s="8"/>
       <c r="T54" s="8"/>
       <c r="U54" s="8" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="V54" s="8"/>
       <c r="W54" s="8"/>
@@ -4191,12 +3945,12 @@
       <c r="AI54" s="8"/>
       <c r="AJ54" s="8"/>
     </row>
-    <row r="55" ht="15.75" customHeight="1">
+    <row r="55" spans="1:36" ht="15.75" customHeight="1">
       <c r="A55" s="7" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B55" s="7" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C55" s="8" t="s">
         <v>36</v>
@@ -4219,7 +3973,7 @@
       <c r="S55" s="8"/>
       <c r="T55" s="8"/>
       <c r="U55" s="8" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="V55" s="8"/>
       <c r="W55" s="8"/>
@@ -4237,12 +3991,12 @@
       <c r="AI55" s="8"/>
       <c r="AJ55" s="8"/>
     </row>
-    <row r="56" ht="15.75" customHeight="1">
+    <row r="56" spans="1:36" ht="15.75" customHeight="1">
       <c r="A56" s="7" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="B56" s="7" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C56" s="8" t="s">
         <v>36</v>
@@ -4265,7 +4019,7 @@
       <c r="S56" s="8"/>
       <c r="T56" s="8"/>
       <c r="U56" s="8" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="V56" s="8"/>
       <c r="W56" s="8"/>
@@ -4283,12 +4037,12 @@
       <c r="AI56" s="8"/>
       <c r="AJ56" s="8"/>
     </row>
-    <row r="57" ht="15.75" customHeight="1">
+    <row r="57" spans="1:36" ht="15.75" customHeight="1">
       <c r="A57" s="7" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B57" s="7" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C57" s="8" t="s">
         <v>36</v>
@@ -4311,7 +4065,7 @@
       <c r="S57" s="8"/>
       <c r="T57" s="8"/>
       <c r="U57" s="8" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="V57" s="8"/>
       <c r="W57" s="8"/>
@@ -4329,9 +4083,9 @@
       <c r="AI57" s="8"/>
       <c r="AJ57" s="8"/>
     </row>
-    <row r="58" ht="15.75" customHeight="1">
+    <row r="58" spans="1:36" ht="15.75" customHeight="1">
       <c r="A58" s="7" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B58" s="7"/>
       <c r="C58" s="8"/>
@@ -4369,9 +4123,9 @@
       <c r="AI58" s="8"/>
       <c r="AJ58" s="8"/>
     </row>
-    <row r="59" ht="15.75" customHeight="1">
+    <row r="59" spans="1:36" ht="15.75" customHeight="1">
       <c r="A59" s="7" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B59" s="7"/>
       <c r="C59" s="8"/>
@@ -4409,7 +4163,7 @@
       <c r="AI59" s="8"/>
       <c r="AJ59" s="8"/>
     </row>
-    <row r="60" ht="15.75" customHeight="1">
+    <row r="60" spans="1:36" ht="15.75" customHeight="1">
       <c r="A60" s="4"/>
       <c r="B60" s="4"/>
       <c r="C60" s="4"/>
@@ -4421,12 +4175,12 @@
       <c r="AI60" s="4"/>
       <c r="AJ60" s="4"/>
     </row>
-    <row r="61" ht="15.75" customHeight="1">
+    <row r="61" spans="1:36" ht="15.75" customHeight="1">
       <c r="A61" s="10" t="s">
         <v>34</v>
       </c>
       <c r="B61" s="10" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C61" s="11" t="s">
         <v>36</v>
@@ -4469,12 +4223,12 @@
       <c r="AI61" s="11"/>
       <c r="AJ61" s="11"/>
     </row>
-    <row r="62" ht="15.75" customHeight="1">
+    <row r="62" spans="1:36" ht="15.75" customHeight="1">
       <c r="A62" s="10" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B62" s="10" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C62" s="11" t="s">
         <v>36</v>
@@ -4497,7 +4251,7 @@
       <c r="S62" s="11"/>
       <c r="T62" s="11"/>
       <c r="U62" s="11" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="V62" s="11"/>
       <c r="W62" s="11"/>
@@ -4512,17 +4266,17 @@
       <c r="AF62" s="12"/>
       <c r="AG62" s="11"/>
       <c r="AH62" s="11" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="AI62" s="11"/>
       <c r="AJ62" s="11"/>
     </row>
-    <row r="63" ht="15.75" customHeight="1">
+    <row r="63" spans="1:36" ht="15.75" customHeight="1">
       <c r="A63" s="10" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B63" s="10" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C63" s="11" t="s">
         <v>36</v>
@@ -4545,7 +4299,7 @@
       <c r="S63" s="11"/>
       <c r="T63" s="11"/>
       <c r="U63" s="11" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="V63" s="11"/>
       <c r="W63" s="11"/>
@@ -4560,17 +4314,17 @@
       <c r="AF63" s="12"/>
       <c r="AG63" s="11"/>
       <c r="AH63" s="11" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="AI63" s="11"/>
       <c r="AJ63" s="11"/>
     </row>
-    <row r="64" ht="15.75" customHeight="1">
+    <row r="64" spans="1:36" ht="15.75" customHeight="1">
       <c r="A64" s="10" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B64" s="10" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C64" s="11" t="s">
         <v>36</v>
@@ -4593,7 +4347,7 @@
       <c r="S64" s="11"/>
       <c r="T64" s="11"/>
       <c r="U64" s="11" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="V64" s="11"/>
       <c r="W64" s="11"/>
@@ -4608,17 +4362,17 @@
       <c r="AF64" s="12"/>
       <c r="AG64" s="11"/>
       <c r="AH64" s="11" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="AI64" s="11"/>
       <c r="AJ64" s="11"/>
     </row>
-    <row r="65" ht="15.75" customHeight="1">
+    <row r="65" spans="1:36" ht="15.75" customHeight="1">
       <c r="A65" s="10" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B65" s="10" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C65" s="11" t="s">
         <v>36</v>
@@ -4641,7 +4395,7 @@
       <c r="S65" s="11"/>
       <c r="T65" s="11"/>
       <c r="U65" s="11" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="V65" s="11"/>
       <c r="W65" s="11"/>
@@ -4656,17 +4410,17 @@
       <c r="AF65" s="12"/>
       <c r="AG65" s="11"/>
       <c r="AH65" s="11" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="AI65" s="11"/>
       <c r="AJ65" s="11"/>
     </row>
-    <row r="66" ht="15.75" customHeight="1">
+    <row r="66" spans="1:36" ht="15.75" customHeight="1">
       <c r="A66" s="10" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B66" s="10" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C66" s="11" t="s">
         <v>36</v>
@@ -4689,7 +4443,7 @@
       <c r="S66" s="11"/>
       <c r="T66" s="11"/>
       <c r="U66" s="11" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="V66" s="11"/>
       <c r="W66" s="11"/>
@@ -4704,17 +4458,17 @@
       <c r="AF66" s="12"/>
       <c r="AG66" s="11"/>
       <c r="AH66" s="11" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="AI66" s="11"/>
       <c r="AJ66" s="11"/>
     </row>
-    <row r="67" ht="15.75" customHeight="1">
+    <row r="67" spans="1:36" ht="15.75" customHeight="1">
       <c r="A67" s="10" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B67" s="10" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C67" s="11" t="s">
         <v>36</v>
@@ -4737,7 +4491,7 @@
       <c r="S67" s="11"/>
       <c r="T67" s="11"/>
       <c r="U67" s="11" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="V67" s="11"/>
       <c r="W67" s="11"/>
@@ -4752,17 +4506,17 @@
       <c r="AF67" s="12"/>
       <c r="AG67" s="11"/>
       <c r="AH67" s="11" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="AI67" s="11"/>
       <c r="AJ67" s="11"/>
     </row>
-    <row r="68" ht="15.75" customHeight="1">
+    <row r="68" spans="1:36" ht="15.75" customHeight="1">
       <c r="A68" s="10" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B68" s="10" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="C68" s="11" t="s">
         <v>36</v>
@@ -4785,7 +4539,7 @@
       <c r="S68" s="11"/>
       <c r="T68" s="11"/>
       <c r="U68" s="11" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="V68" s="11"/>
       <c r="W68" s="11"/>
@@ -4800,17 +4554,17 @@
       <c r="AF68" s="12"/>
       <c r="AG68" s="11"/>
       <c r="AH68" s="11" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="AI68" s="11"/>
       <c r="AJ68" s="11"/>
     </row>
-    <row r="69" ht="15.75" customHeight="1">
+    <row r="69" spans="1:36" ht="15.75" customHeight="1">
       <c r="A69" s="10" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B69" s="10" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C69" s="11" t="s">
         <v>36</v>
@@ -4833,7 +4587,7 @@
       <c r="S69" s="11"/>
       <c r="T69" s="11"/>
       <c r="U69" s="11" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="V69" s="11"/>
       <c r="W69" s="11"/>
@@ -4848,17 +4602,17 @@
       <c r="AF69" s="12"/>
       <c r="AG69" s="11"/>
       <c r="AH69" s="11" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="AI69" s="11"/>
       <c r="AJ69" s="11"/>
     </row>
-    <row r="70" ht="15.75" customHeight="1">
+    <row r="70" spans="1:36" ht="15.75" customHeight="1">
       <c r="A70" s="10" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B70" s="10" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="C70" s="11" t="s">
         <v>36</v>
@@ -4881,7 +4635,7 @@
       <c r="S70" s="11"/>
       <c r="T70" s="11"/>
       <c r="U70" s="11" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="V70" s="11"/>
       <c r="W70" s="11"/>
@@ -4896,17 +4650,17 @@
       <c r="AF70" s="12"/>
       <c r="AG70" s="11"/>
       <c r="AH70" s="11" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="AI70" s="11"/>
       <c r="AJ70" s="11"/>
     </row>
-    <row r="71" ht="15.75" customHeight="1">
+    <row r="71" spans="1:36" ht="15.75" customHeight="1">
       <c r="A71" s="10" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B71" s="10" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C71" s="11" t="s">
         <v>36</v>
@@ -4929,7 +4683,7 @@
       <c r="S71" s="11"/>
       <c r="T71" s="11"/>
       <c r="U71" s="11" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="V71" s="11"/>
       <c r="W71" s="11"/>
@@ -4944,17 +4698,17 @@
       <c r="AF71" s="12"/>
       <c r="AG71" s="11"/>
       <c r="AH71" s="11" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="AI71" s="11"/>
       <c r="AJ71" s="11"/>
     </row>
-    <row r="72" ht="15.75" customHeight="1">
+    <row r="72" spans="1:36" ht="15.75" customHeight="1">
       <c r="A72" s="10" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B72" s="10" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="C72" s="11" t="s">
         <v>36</v>
@@ -4977,7 +4731,7 @@
       <c r="S72" s="11"/>
       <c r="T72" s="11"/>
       <c r="U72" s="11" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="V72" s="11"/>
       <c r="W72" s="11"/>
@@ -4992,17 +4746,17 @@
       <c r="AF72" s="12"/>
       <c r="AG72" s="11"/>
       <c r="AH72" s="11" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="AI72" s="11"/>
       <c r="AJ72" s="11"/>
     </row>
-    <row r="73" ht="15.75" customHeight="1">
+    <row r="73" spans="1:36" ht="15.75" customHeight="1">
       <c r="A73" s="10" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B73" s="10" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C73" s="11" t="s">
         <v>36</v>
@@ -5025,7 +4779,7 @@
       <c r="S73" s="11"/>
       <c r="T73" s="11"/>
       <c r="U73" s="11" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="V73" s="11"/>
       <c r="W73" s="11"/>
@@ -5040,17 +4794,17 @@
       <c r="AF73" s="12"/>
       <c r="AG73" s="11"/>
       <c r="AH73" s="11" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="AI73" s="11"/>
       <c r="AJ73" s="11"/>
     </row>
-    <row r="74" ht="15.75" customHeight="1">
+    <row r="74" spans="1:36" ht="15.75" customHeight="1">
       <c r="A74" s="10" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B74" s="10" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C74" s="11" t="s">
         <v>36</v>
@@ -5073,7 +4827,7 @@
       <c r="S74" s="11"/>
       <c r="T74" s="11"/>
       <c r="U74" s="11" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="V74" s="11"/>
       <c r="W74" s="11"/>
@@ -5088,17 +4842,17 @@
       <c r="AF74" s="12"/>
       <c r="AG74" s="11"/>
       <c r="AH74" s="11" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="AI74" s="11"/>
       <c r="AJ74" s="11"/>
     </row>
-    <row r="75" ht="15.75" customHeight="1">
+    <row r="75" spans="1:36" ht="15.75" customHeight="1">
       <c r="A75" s="10" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B75" s="10" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="C75" s="11" t="s">
         <v>36</v>
@@ -5121,7 +4875,7 @@
       <c r="S75" s="11"/>
       <c r="T75" s="11"/>
       <c r="U75" s="11" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="V75" s="11"/>
       <c r="W75" s="11"/>
@@ -5136,17 +4890,17 @@
       <c r="AF75" s="12"/>
       <c r="AG75" s="11"/>
       <c r="AH75" s="11" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="AI75" s="11"/>
       <c r="AJ75" s="11"/>
     </row>
-    <row r="76" ht="15.75" customHeight="1">
+    <row r="76" spans="1:36" ht="15.75" customHeight="1">
       <c r="A76" s="13" t="s">
         <v>34</v>
       </c>
       <c r="B76" s="13" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C76" s="11" t="s">
         <v>36</v>
@@ -5185,12 +4939,12 @@
       <c r="AI76" s="14"/>
       <c r="AJ76" s="14"/>
     </row>
-    <row r="77" ht="15.75" customHeight="1">
+    <row r="77" spans="1:36" ht="15.75" customHeight="1">
       <c r="A77" s="10" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B77" s="10" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C77" s="11" t="s">
         <v>36</v>
@@ -5213,7 +4967,7 @@
       <c r="S77" s="11"/>
       <c r="T77" s="11"/>
       <c r="U77" s="14" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="V77" s="11"/>
       <c r="W77" s="11"/>
@@ -5228,17 +4982,17 @@
       <c r="AF77" s="12"/>
       <c r="AG77" s="11"/>
       <c r="AH77" s="14" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="AI77" s="11"/>
       <c r="AJ77" s="11"/>
     </row>
-    <row r="78" ht="15.75" customHeight="1">
+    <row r="78" spans="1:36" ht="15.75" customHeight="1">
       <c r="A78" s="10" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B78" s="10" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C78" s="11" t="s">
         <v>36</v>
@@ -5261,7 +5015,7 @@
       <c r="S78" s="11"/>
       <c r="T78" s="11"/>
       <c r="U78" s="14" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="V78" s="11"/>
       <c r="W78" s="11"/>
@@ -5276,17 +5030,17 @@
       <c r="AF78" s="12"/>
       <c r="AG78" s="11"/>
       <c r="AH78" s="14" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="AI78" s="11"/>
       <c r="AJ78" s="11"/>
     </row>
-    <row r="79" ht="15.75" customHeight="1">
+    <row r="79" spans="1:36" ht="15.75" customHeight="1">
       <c r="A79" s="10" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B79" s="10" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C79" s="11" t="s">
         <v>36</v>
@@ -5309,7 +5063,7 @@
       <c r="S79" s="11"/>
       <c r="T79" s="11"/>
       <c r="U79" s="14" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="V79" s="11"/>
       <c r="W79" s="11"/>
@@ -5324,17 +5078,17 @@
       <c r="AF79" s="12"/>
       <c r="AG79" s="11"/>
       <c r="AH79" s="14" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="AI79" s="11"/>
       <c r="AJ79" s="11"/>
     </row>
-    <row r="80" ht="15.75" customHeight="1">
+    <row r="80" spans="1:36" ht="15.75" customHeight="1">
       <c r="A80" s="10" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B80" s="10" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="C80" s="11" t="s">
         <v>36</v>
@@ -5357,7 +5111,7 @@
       <c r="S80" s="11"/>
       <c r="T80" s="11"/>
       <c r="U80" s="14" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="V80" s="11"/>
       <c r="W80" s="11"/>
@@ -5377,12 +5131,12 @@
       <c r="AI80" s="11"/>
       <c r="AJ80" s="11"/>
     </row>
-    <row r="81" ht="15.75" customHeight="1">
+    <row r="81" spans="1:36" ht="15.75" customHeight="1">
       <c r="A81" s="10" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B81" s="10" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C81" s="11" t="s">
         <v>36</v>
@@ -5405,7 +5159,7 @@
       <c r="S81" s="11"/>
       <c r="T81" s="11"/>
       <c r="U81" s="14" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="V81" s="11"/>
       <c r="W81" s="11"/>
@@ -5420,17 +5174,17 @@
       <c r="AF81" s="12"/>
       <c r="AG81" s="11"/>
       <c r="AH81" s="14" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="AI81" s="11"/>
       <c r="AJ81" s="11"/>
     </row>
-    <row r="82" ht="15.75" customHeight="1">
+    <row r="82" spans="1:36" ht="15.75" customHeight="1">
       <c r="A82" s="10" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B82" s="10" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C82" s="11" t="s">
         <v>36</v>
@@ -5453,7 +5207,7 @@
       <c r="S82" s="11"/>
       <c r="T82" s="11"/>
       <c r="U82" s="11" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="V82" s="11"/>
       <c r="W82" s="11"/>
@@ -5468,17 +5222,17 @@
       <c r="AF82" s="12"/>
       <c r="AG82" s="11"/>
       <c r="AH82" s="14" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="AI82" s="11"/>
       <c r="AJ82" s="11"/>
     </row>
-    <row r="83" ht="15.75" customHeight="1">
+    <row r="83" spans="1:36" ht="15.75" customHeight="1">
       <c r="A83" s="13" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B83" s="13" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C83" s="14"/>
       <c r="D83" s="14"/>
@@ -5515,12 +5269,12 @@
       <c r="AI83" s="14"/>
       <c r="AJ83" s="14"/>
     </row>
-    <row r="84" ht="15.75" customHeight="1">
+    <row r="84" spans="1:36" ht="15.75" customHeight="1">
       <c r="A84" s="13" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B84" s="13" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C84" s="14"/>
       <c r="D84" s="14"/>
@@ -5557,7 +5311,7 @@
       <c r="AI84" s="14"/>
       <c r="AJ84" s="14"/>
     </row>
-    <row r="85" ht="15.75" customHeight="1">
+    <row r="85" spans="1:36" ht="15.75" customHeight="1">
       <c r="A85" s="13"/>
       <c r="B85" s="13"/>
       <c r="C85" s="14"/>
@@ -5595,7 +5349,7 @@
       <c r="AI85" s="14"/>
       <c r="AJ85" s="14"/>
     </row>
-    <row r="86" ht="15.75" customHeight="1">
+    <row r="86" spans="1:36" ht="15.75" customHeight="1">
       <c r="A86" s="13"/>
       <c r="B86" s="13"/>
       <c r="C86" s="14"/>
@@ -5633,7 +5387,7 @@
       <c r="AI86" s="14"/>
       <c r="AJ86" s="14"/>
     </row>
-    <row r="87" ht="15.75" customHeight="1">
+    <row r="87" spans="1:36" ht="15.75" customHeight="1">
       <c r="A87" s="13"/>
       <c r="B87" s="13"/>
       <c r="C87" s="14"/>
@@ -5671,7 +5425,7 @@
       <c r="AI87" s="14"/>
       <c r="AJ87" s="14"/>
     </row>
-    <row r="88" ht="15.75" customHeight="1">
+    <row r="88" spans="1:36" ht="15.75" customHeight="1">
       <c r="A88" s="13"/>
       <c r="B88" s="13"/>
       <c r="C88" s="14"/>
@@ -5709,7 +5463,7 @@
       <c r="AI88" s="14"/>
       <c r="AJ88" s="14"/>
     </row>
-    <row r="89" ht="15.75" customHeight="1">
+    <row r="89" spans="1:36" ht="15.75" customHeight="1">
       <c r="A89" s="13"/>
       <c r="B89" s="13"/>
       <c r="C89" s="14"/>
@@ -5747,7 +5501,7 @@
       <c r="AI89" s="14"/>
       <c r="AJ89" s="14"/>
     </row>
-    <row r="90" ht="15.75" customHeight="1">
+    <row r="90" spans="1:36" ht="15.75" customHeight="1">
       <c r="A90" s="13"/>
       <c r="B90" s="13"/>
       <c r="C90" s="14"/>
@@ -5785,7 +5539,7 @@
       <c r="AI90" s="14"/>
       <c r="AJ90" s="14"/>
     </row>
-    <row r="91" ht="15.75" customHeight="1">
+    <row r="91" spans="1:36" ht="15.75" customHeight="1">
       <c r="A91" s="13"/>
       <c r="B91" s="13"/>
       <c r="C91" s="14"/>
@@ -5823,7 +5577,7 @@
       <c r="AI91" s="14"/>
       <c r="AJ91" s="14"/>
     </row>
-    <row r="92" ht="15.75" customHeight="1">
+    <row r="92" spans="1:36" ht="15.75" customHeight="1">
       <c r="A92" s="13"/>
       <c r="B92" s="13"/>
       <c r="C92" s="14"/>
@@ -5861,7 +5615,7 @@
       <c r="AI92" s="14"/>
       <c r="AJ92" s="14"/>
     </row>
-    <row r="93" ht="15.75" customHeight="1">
+    <row r="93" spans="1:36" ht="15.75" customHeight="1">
       <c r="A93" s="13"/>
       <c r="B93" s="13"/>
       <c r="C93" s="14"/>
@@ -5899,7 +5653,7 @@
       <c r="AI93" s="14"/>
       <c r="AJ93" s="14"/>
     </row>
-    <row r="94" ht="15.75" customHeight="1">
+    <row r="94" spans="1:36" ht="15.75" customHeight="1">
       <c r="A94" s="13"/>
       <c r="B94" s="13"/>
       <c r="C94" s="14"/>
@@ -5937,7 +5691,7 @@
       <c r="AI94" s="14"/>
       <c r="AJ94" s="14"/>
     </row>
-    <row r="95" ht="15.75" customHeight="1">
+    <row r="95" spans="1:36" ht="15.75" customHeight="1">
       <c r="A95" s="13"/>
       <c r="B95" s="13"/>
       <c r="C95" s="14"/>
@@ -5975,7 +5729,7 @@
       <c r="AI95" s="14"/>
       <c r="AJ95" s="14"/>
     </row>
-    <row r="96" ht="15.75" customHeight="1">
+    <row r="96" spans="1:36" ht="15.75" customHeight="1">
       <c r="A96" s="13"/>
       <c r="B96" s="13"/>
       <c r="C96" s="14"/>
@@ -6013,7 +5767,7 @@
       <c r="AI96" s="14"/>
       <c r="AJ96" s="14"/>
     </row>
-    <row r="97" ht="15.75" customHeight="1">
+    <row r="97" spans="1:36" ht="15.75" customHeight="1">
       <c r="A97" s="13"/>
       <c r="B97" s="13"/>
       <c r="C97" s="14"/>
@@ -6052,41 +5806,32 @@
       <c r="AJ97" s="14"/>
     </row>
   </sheetData>
-  <printOptions headings="0" gridLines="0"/>
-  <pageMargins left="0.70078740157480324" right="0.70078740157480324" top="0.75196850393700787" bottom="0.75196850393700787" header="0.29999999999999999" footer="0.29999999999999999"/>
-  <pageSetup paperSize="9" scale="100" firstPageNumber="2147483648" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
-  <headerFooter/>
-  <legacyDrawing r:id="rId3"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1" disablePrompts="0">
-        <x14:dataValidation xr:uid="{00DB0042-004C-4504-B0B2-00A400CF007D}" type="list" allowBlank="1" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="0" showInputMessage="0">
-          <x14:formula1>
-            <xm:f>"yes,no"</xm:f>
-          </x14:formula1>
-          <xm:sqref>J2:J97</xm:sqref>
-        </x14:dataValidation>
-      </x14:dataValidations>
-    </ext>
-  </extLst>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" sqref="J2:J97" xr:uid="{00DB0042-004C-4504-B0B2-00A400CF007D}">
+      <formula1>"yes,no"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.70078740157480324" right="0.70078740157480324" top="0.75196850393700787" bottom="0.75196850393700787" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" firstPageNumber="2147483648" orientation="portrait"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
-    <outlinePr applyStyles="0" summaryBelow="0" summaryRight="0" showOutlineSymbols="1"/>
-    <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr defaultColWidth="14.43" defaultRowHeight="15" customHeight="1"/>
+  <dimension ref="A1:V67"/>
+  <sheetFormatPr defaultColWidth="14.44140625" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="28.289999999999999"/>
-    <col customWidth="1" min="2" max="22" width="45.859999999999999"/>
+    <col min="1" max="1" width="28.33203125" customWidth="1"/>
+    <col min="2" max="22" width="45.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.75" customHeight="1">
+    <row r="1" spans="1:22" ht="15.75" customHeight="1">
       <c r="A1" s="15" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B1" s="15" t="s">
         <v>1</v>
@@ -6126,15 +5871,15 @@
       <c r="U1" s="23"/>
       <c r="V1" s="23"/>
     </row>
-    <row r="2" ht="15.75" customHeight="1">
+    <row r="2" spans="1:22" ht="15.75" customHeight="1">
       <c r="A2" s="23" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B2" s="23" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C2" s="24" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="D2" s="25"/>
       <c r="E2" s="25"/>
@@ -6156,15 +5901,15 @@
       <c r="U2" s="25"/>
       <c r="V2" s="25"/>
     </row>
-    <row r="3" ht="15.75" customHeight="1">
+    <row r="3" spans="1:22" ht="15.75" customHeight="1">
       <c r="A3" s="23" t="s">
+        <v>203</v>
+      </c>
+      <c r="B3" s="23" t="s">
         <v>205</v>
       </c>
-      <c r="B3" s="23" t="s">
-        <v>207</v>
-      </c>
       <c r="C3" s="24" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="D3" s="25"/>
       <c r="E3" s="25"/>
@@ -6186,7 +5931,7 @@
       <c r="U3" s="25"/>
       <c r="V3" s="25"/>
     </row>
-    <row r="4" ht="15.75" customHeight="1">
+    <row r="4" spans="1:22" ht="15.75" customHeight="1">
       <c r="A4" s="23"/>
       <c r="B4" s="23"/>
       <c r="C4" s="24"/>
@@ -6210,254 +5955,252 @@
       <c r="U4" s="25"/>
       <c r="V4" s="25"/>
     </row>
-    <row r="5" ht="15.75" customHeight="1">
+    <row r="5" spans="1:22" ht="15.75" customHeight="1">
       <c r="A5" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>208</v>
+      </c>
+      <c r="C5" s="25" t="s">
         <v>209</v>
       </c>
-      <c r="B5" s="4" t="s">
+    </row>
+    <row r="6" spans="1:22" ht="15.75" customHeight="1">
+      <c r="A6" s="4" t="s">
         <v>210</v>
       </c>
-      <c r="C5" s="25" t="s">
+      <c r="B6" s="4" t="s">
         <v>211</v>
       </c>
-    </row>
-    <row r="6" ht="15.75" customHeight="1">
-      <c r="A6" s="4" t="s">
+      <c r="C6" s="25" t="s">
         <v>212</v>
       </c>
-      <c r="B6" s="4" t="s">
-        <v>213</v>
-      </c>
-      <c r="C6" s="25" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="7" ht="15.75" customHeight="1">
+    </row>
+    <row r="7" spans="1:22" ht="15.75" customHeight="1">
       <c r="C7" s="25"/>
     </row>
-    <row r="8" ht="15.75" customHeight="1">
+    <row r="8" spans="1:22" ht="15.75" customHeight="1">
       <c r="C8" s="25"/>
     </row>
-    <row r="9" ht="15.75" customHeight="1">
+    <row r="9" spans="1:22" ht="15.75" customHeight="1">
       <c r="C9" s="25"/>
     </row>
-    <row r="10" ht="15.75" customHeight="1">
+    <row r="10" spans="1:22" ht="15.75" customHeight="1">
       <c r="C10" s="25"/>
     </row>
-    <row r="11" ht="15.75" customHeight="1">
+    <row r="11" spans="1:22" ht="15.75" customHeight="1">
       <c r="C11" s="25"/>
     </row>
-    <row r="12" ht="15.75" customHeight="1">
+    <row r="12" spans="1:22" ht="15.75" customHeight="1">
       <c r="C12" s="25"/>
     </row>
-    <row r="13" ht="15.75" customHeight="1">
+    <row r="13" spans="1:22" ht="15.75" customHeight="1">
       <c r="C13" s="25"/>
     </row>
-    <row r="14" ht="15.75" customHeight="1">
+    <row r="14" spans="1:22" ht="15.75" customHeight="1">
       <c r="C14" s="25"/>
     </row>
-    <row r="15" ht="15.75" customHeight="1">
+    <row r="15" spans="1:22" ht="15.75" customHeight="1">
       <c r="C15" s="25"/>
     </row>
-    <row r="16" ht="15.75" customHeight="1">
+    <row r="16" spans="1:22" ht="15.75" customHeight="1">
       <c r="C16" s="25"/>
     </row>
-    <row r="17" ht="15.75" customHeight="1">
+    <row r="17" spans="3:3" ht="15.75" customHeight="1">
       <c r="C17" s="25"/>
     </row>
-    <row r="18" ht="15.75" customHeight="1">
+    <row r="18" spans="3:3" ht="15.75" customHeight="1">
       <c r="C18" s="25"/>
     </row>
-    <row r="19" ht="15.75" customHeight="1">
+    <row r="19" spans="3:3" ht="15.75" customHeight="1">
       <c r="C19" s="25"/>
     </row>
-    <row r="20" ht="15.75" customHeight="1">
+    <row r="20" spans="3:3" ht="15.75" customHeight="1">
       <c r="C20" s="25"/>
     </row>
-    <row r="21" ht="15.75" customHeight="1">
+    <row r="21" spans="3:3" ht="15.75" customHeight="1">
       <c r="C21" s="25"/>
     </row>
-    <row r="22" ht="15.75" customHeight="1">
+    <row r="22" spans="3:3" ht="15.75" customHeight="1">
       <c r="C22" s="25"/>
     </row>
-    <row r="23" ht="15.75" customHeight="1">
+    <row r="23" spans="3:3" ht="15.75" customHeight="1">
       <c r="C23" s="25"/>
     </row>
-    <row r="24" ht="15.75" customHeight="1">
+    <row r="24" spans="3:3" ht="15.75" customHeight="1">
       <c r="C24" s="25"/>
     </row>
-    <row r="25" ht="15.75" customHeight="1">
+    <row r="25" spans="3:3" ht="15.75" customHeight="1">
       <c r="C25" s="25"/>
     </row>
-    <row r="26" ht="15.75" customHeight="1">
+    <row r="26" spans="3:3" ht="15.75" customHeight="1">
       <c r="C26" s="25"/>
     </row>
-    <row r="27" ht="15.75" customHeight="1">
+    <row r="27" spans="3:3" ht="15.75" customHeight="1">
       <c r="C27" s="25"/>
     </row>
-    <row r="28" ht="15.75" customHeight="1">
+    <row r="28" spans="3:3" ht="15.75" customHeight="1">
       <c r="C28" s="25"/>
     </row>
-    <row r="29" ht="15.75" customHeight="1">
+    <row r="29" spans="3:3" ht="15.75" customHeight="1">
       <c r="C29" s="25"/>
     </row>
-    <row r="30" ht="15.75" customHeight="1">
+    <row r="30" spans="3:3" ht="15.75" customHeight="1">
       <c r="C30" s="25"/>
     </row>
-    <row r="31" ht="15.75" customHeight="1">
+    <row r="31" spans="3:3" ht="15.75" customHeight="1">
       <c r="C31" s="25"/>
     </row>
-    <row r="32" ht="15.75" customHeight="1">
+    <row r="32" spans="3:3" ht="15.75" customHeight="1">
       <c r="C32" s="25"/>
     </row>
-    <row r="33" ht="15.75" customHeight="1">
+    <row r="33" spans="3:3" ht="15.75" customHeight="1">
       <c r="C33" s="25"/>
     </row>
-    <row r="34" ht="15.75" customHeight="1">
+    <row r="34" spans="3:3" ht="15.75" customHeight="1">
       <c r="C34" s="25"/>
     </row>
-    <row r="35" ht="15.75" customHeight="1">
+    <row r="35" spans="3:3" ht="15.75" customHeight="1">
       <c r="C35" s="25"/>
     </row>
-    <row r="36" ht="15.75" customHeight="1">
+    <row r="36" spans="3:3" ht="15.75" customHeight="1">
       <c r="C36" s="25"/>
     </row>
-    <row r="37" ht="15.75" customHeight="1">
+    <row r="37" spans="3:3" ht="15.75" customHeight="1">
       <c r="C37" s="25"/>
     </row>
-    <row r="38" ht="15.75" customHeight="1">
+    <row r="38" spans="3:3" ht="15.75" customHeight="1">
       <c r="C38" s="25"/>
     </row>
-    <row r="39" ht="15.75" customHeight="1">
+    <row r="39" spans="3:3" ht="15.75" customHeight="1">
       <c r="C39" s="25"/>
     </row>
-    <row r="40" ht="15.75" customHeight="1">
+    <row r="40" spans="3:3" ht="15.75" customHeight="1">
       <c r="C40" s="25"/>
     </row>
-    <row r="41" ht="15.75" customHeight="1">
+    <row r="41" spans="3:3" ht="15.75" customHeight="1">
       <c r="C41" s="25"/>
     </row>
-    <row r="42" ht="15.75" customHeight="1">
+    <row r="42" spans="3:3" ht="15.75" customHeight="1">
       <c r="C42" s="25"/>
     </row>
-    <row r="43" ht="15.75" customHeight="1">
+    <row r="43" spans="3:3" ht="15.75" customHeight="1">
       <c r="C43" s="25"/>
     </row>
-    <row r="44" ht="15.75" customHeight="1">
+    <row r="44" spans="3:3" ht="15.75" customHeight="1">
       <c r="C44" s="25"/>
     </row>
-    <row r="45" ht="15.75" customHeight="1">
+    <row r="45" spans="3:3" ht="15.75" customHeight="1">
       <c r="C45" s="25"/>
     </row>
-    <row r="46" ht="15.75" customHeight="1">
+    <row r="46" spans="3:3" ht="15.75" customHeight="1">
       <c r="C46" s="25"/>
     </row>
-    <row r="47" ht="15.75" customHeight="1">
+    <row r="47" spans="3:3" ht="15.75" customHeight="1">
       <c r="C47" s="25"/>
     </row>
-    <row r="48" ht="15.75" customHeight="1">
+    <row r="48" spans="3:3" ht="15.75" customHeight="1">
       <c r="C48" s="25"/>
     </row>
-    <row r="49" ht="15.75" customHeight="1">
+    <row r="49" spans="3:3" ht="15.75" customHeight="1">
       <c r="C49" s="25"/>
     </row>
-    <row r="50" ht="15.75" customHeight="1">
+    <row r="50" spans="3:3" ht="15.75" customHeight="1">
       <c r="C50" s="25"/>
     </row>
-    <row r="51" ht="15.75" customHeight="1">
+    <row r="51" spans="3:3" ht="15.75" customHeight="1">
       <c r="C51" s="25"/>
     </row>
-    <row r="52" ht="15.75" customHeight="1">
+    <row r="52" spans="3:3" ht="15.75" customHeight="1">
       <c r="C52" s="25"/>
     </row>
-    <row r="53" ht="15.75" customHeight="1">
+    <row r="53" spans="3:3" ht="15.75" customHeight="1">
       <c r="C53" s="25"/>
     </row>
-    <row r="54" ht="15.75" customHeight="1">
+    <row r="54" spans="3:3" ht="15.75" customHeight="1">
       <c r="C54" s="25"/>
     </row>
-    <row r="55" ht="15.75" customHeight="1">
+    <row r="55" spans="3:3" ht="15.75" customHeight="1">
       <c r="C55" s="25"/>
     </row>
-    <row r="56" ht="15.75" customHeight="1">
+    <row r="56" spans="3:3" ht="15.75" customHeight="1">
       <c r="C56" s="25"/>
     </row>
-    <row r="57" ht="15.75" customHeight="1">
+    <row r="57" spans="3:3" ht="15.75" customHeight="1">
       <c r="C57" s="25"/>
     </row>
-    <row r="58" ht="15.75" customHeight="1">
+    <row r="58" spans="3:3" ht="15.75" customHeight="1">
       <c r="C58" s="25"/>
     </row>
-    <row r="59" ht="15.75" customHeight="1">
+    <row r="59" spans="3:3" ht="15.75" customHeight="1">
       <c r="C59" s="25"/>
     </row>
-    <row r="60" ht="15.75" customHeight="1">
+    <row r="60" spans="3:3" ht="15.75" customHeight="1">
       <c r="C60" s="25"/>
     </row>
-    <row r="61" ht="15.75" customHeight="1">
+    <row r="61" spans="3:3" ht="15.75" customHeight="1">
       <c r="C61" s="25"/>
     </row>
-    <row r="62" ht="15.75" customHeight="1">
+    <row r="62" spans="3:3" ht="15.75" customHeight="1">
       <c r="C62" s="25"/>
     </row>
-    <row r="63" ht="15.75" customHeight="1">
+    <row r="63" spans="3:3" ht="15.75" customHeight="1">
       <c r="C63" s="25"/>
     </row>
-    <row r="64" ht="15.75" customHeight="1">
+    <row r="64" spans="3:3" ht="15.75" customHeight="1">
       <c r="C64" s="25"/>
     </row>
-    <row r="65" ht="15.75" customHeight="1">
+    <row r="65" spans="3:3" ht="15.75" customHeight="1">
       <c r="C65" s="25"/>
     </row>
-    <row r="66" ht="15.75" customHeight="1">
+    <row r="66" spans="3:3" ht="15.75" customHeight="1">
       <c r="C66" s="25"/>
     </row>
-    <row r="67" ht="15.75" customHeight="1">
+    <row r="67" spans="3:3" ht="15.75" customHeight="1">
       <c r="C67" s="25"/>
     </row>
   </sheetData>
-  <printOptions headings="0" gridLines="0"/>
-  <pageMargins left="0.70078740157480324" right="0.70078740157480324" top="0.75196850393700787" bottom="0.75196850393700787" header="0.29999999999999999" footer="0.29999999999999999"/>
-  <pageSetup paperSize="9" scale="100" firstPageNumber="2147483648" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
-  <headerFooter/>
+  <pageMargins left="0.70078740157480324" right="0.70078740157480324" top="0.75196850393700787" bottom="0.75196850393700787" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" firstPageNumber="2147483648" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr>
-    <outlinePr applyStyles="0" summaryBelow="0" summaryRight="0" showOutlineSymbols="1"/>
-    <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr defaultColWidth="14.43" defaultRowHeight="15" customHeight="1"/>
+  <dimension ref="A1:Z2"/>
+  <sheetFormatPr defaultColWidth="14.44140625" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="21"/>
-    <col customWidth="1" min="2" max="2" width="22.710000000000001"/>
-    <col customWidth="1" min="3" max="3" width="24.57"/>
-    <col customWidth="1" min="4" max="6" width="14.43"/>
+    <col min="1" max="1" width="21" customWidth="1"/>
+    <col min="2" max="2" width="22.6640625" customWidth="1"/>
+    <col min="3" max="3" width="24.5546875" customWidth="1"/>
+    <col min="4" max="6" width="14.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.75" customHeight="1">
+    <row r="1" spans="1:26" ht="15.75" customHeight="1">
       <c r="A1" s="15" t="s">
+        <v>213</v>
+      </c>
+      <c r="B1" s="15" t="s">
+        <v>214</v>
+      </c>
+      <c r="C1" s="15" t="s">
         <v>215</v>
       </c>
-      <c r="B1" s="15" t="s">
+      <c r="D1" s="15" t="s">
         <v>216</v>
       </c>
-      <c r="C1" s="15" t="s">
+      <c r="E1" s="15" t="s">
         <v>217</v>
       </c>
-      <c r="D1" s="15" t="s">
+      <c r="F1" s="15" t="s">
         <v>218</v>
       </c>
-      <c r="E1" s="15" t="s">
+      <c r="G1" s="26" t="s">
         <v>219</v>
-      </c>
-      <c r="F1" s="15" t="s">
-        <v>220</v>
-      </c>
-      <c r="G1" s="26" t="s">
-        <v>221</v>
       </c>
       <c r="H1" s="15"/>
       <c r="I1" s="15"/>
@@ -6479,26 +6222,26 @@
       <c r="Y1" s="15"/>
       <c r="Z1" s="15"/>
     </row>
-    <row r="2" ht="15.75" customHeight="1">
+    <row r="2" spans="1:26" ht="15.75" customHeight="1">
       <c r="A2" s="27" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="B2" s="27" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="C2" s="28">
         <f ca="1">NOW()</f>
-        <v>44830.473900462966</v>
+        <v>45778.935157754633</v>
       </c>
       <c r="D2" s="24" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="E2" s="24" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="F2" s="23"/>
       <c r="G2" s="29" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="H2" s="23"/>
       <c r="I2" s="23"/>
@@ -6521,28 +6264,26 @@
       <c r="Z2" s="23"/>
     </row>
   </sheetData>
-  <printOptions headings="0" gridLines="0"/>
-  <pageMargins left="0.70078740157480324" right="0.70078740157480324" top="0.75196850393700787" bottom="0.75196850393700787" header="0.29999999999999999" footer="0.29999999999999999"/>
-  <pageSetup paperSize="9" scale="100" firstPageNumber="2147483648" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
-  <headerFooter/>
+  <pageMargins left="0.70078740157480324" right="0.70078740157480324" top="0.75196850393700787" bottom="0.75196850393700787" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" firstPageNumber="2147483648" orientation="portrait"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr>
-    <outlinePr applyStyles="0" summaryBelow="0" summaryRight="0" showOutlineSymbols="1"/>
-    <pageSetUpPr autoPageBreaks="1" fitToPage="0"/>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr defaultColWidth="14.43" defaultRowHeight="15" customHeight="1"/>
+  <dimension ref="A1:W1000"/>
+  <sheetFormatPr defaultColWidth="14.44140625" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="28.289999999999999"/>
-    <col customWidth="1" min="2" max="23" width="45.859999999999999"/>
+    <col min="1" max="1" width="28.33203125" customWidth="1"/>
+    <col min="2" max="23" width="45.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.75" customHeight="1">
+    <row r="1" spans="1:23" ht="15.75" customHeight="1">
       <c r="A1" s="15" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B1" s="15" t="s">
         <v>1</v>
@@ -6583,15 +6324,15 @@
       <c r="V1" s="23"/>
       <c r="W1" s="23"/>
     </row>
-    <row r="2" ht="15.75" customHeight="1">
+    <row r="2" spans="1:23" ht="15.75" customHeight="1">
       <c r="A2" s="25" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="B2" s="25" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C2" s="25" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="D2" s="25"/>
       <c r="E2" s="25"/>
@@ -6614,15 +6355,15 @@
       <c r="V2" s="25"/>
       <c r="W2" s="25"/>
     </row>
-    <row r="3" ht="15.75" customHeight="1">
+    <row r="3" spans="1:23" ht="15.75" customHeight="1">
       <c r="A3" s="25" t="s">
+        <v>203</v>
+      </c>
+      <c r="B3" s="25" t="s">
         <v>205</v>
       </c>
-      <c r="B3" s="25" t="s">
-        <v>207</v>
-      </c>
       <c r="C3" s="25" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="D3" s="25"/>
       <c r="E3" s="25"/>
@@ -6645,7 +6386,7 @@
       <c r="V3" s="25"/>
       <c r="W3" s="25"/>
     </row>
-    <row r="4" ht="15.75" customHeight="1">
+    <row r="4" spans="1:23" ht="15.75" customHeight="1">
       <c r="A4" s="25"/>
       <c r="B4" s="25"/>
       <c r="C4" s="25"/>
@@ -6670,15 +6411,15 @@
       <c r="V4" s="25"/>
       <c r="W4" s="25"/>
     </row>
-    <row r="5" ht="15.75" customHeight="1">
+    <row r="5" spans="1:23" ht="15.75" customHeight="1">
       <c r="A5" s="25" t="s">
+        <v>224</v>
+      </c>
+      <c r="B5" s="25" t="s">
+        <v>225</v>
+      </c>
+      <c r="C5" s="25" t="s">
         <v>226</v>
-      </c>
-      <c r="B5" s="25" t="s">
-        <v>227</v>
-      </c>
-      <c r="C5" s="25" t="s">
-        <v>228</v>
       </c>
       <c r="D5" s="25"/>
       <c r="E5" s="25"/>
@@ -6701,15 +6442,15 @@
       <c r="V5" s="25"/>
       <c r="W5" s="25"/>
     </row>
-    <row r="6" ht="15.75" customHeight="1">
+    <row r="6" spans="1:23" ht="15.75" customHeight="1">
       <c r="A6" s="25" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="B6" s="25" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C6" s="25" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="D6" s="25"/>
       <c r="E6" s="25"/>
@@ -6732,15 +6473,15 @@
       <c r="V6" s="25"/>
       <c r="W6" s="25"/>
     </row>
-    <row r="7" ht="15.75" customHeight="1">
+    <row r="7" spans="1:23" ht="15.75" customHeight="1">
       <c r="A7" s="25" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="B7" s="25" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C7" s="25" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="D7" s="25"/>
       <c r="E7" s="25"/>
@@ -6763,15 +6504,15 @@
       <c r="V7" s="25"/>
       <c r="W7" s="25"/>
     </row>
-    <row r="8" ht="15.75" customHeight="1">
+    <row r="8" spans="1:23" ht="15.75" customHeight="1">
       <c r="A8" s="25" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="B8" s="25" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="C8" s="25" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="D8" s="25"/>
       <c r="E8" s="25"/>
@@ -6794,15 +6535,15 @@
       <c r="V8" s="25"/>
       <c r="W8" s="25"/>
     </row>
-    <row r="9" ht="15.75" customHeight="1">
+    <row r="9" spans="1:23" ht="15.75" customHeight="1">
       <c r="A9" s="25" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="B9" s="25" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="C9" s="25" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="D9" s="25"/>
       <c r="E9" s="25"/>
@@ -6825,7 +6566,7 @@
       <c r="V9" s="25"/>
       <c r="W9" s="25"/>
     </row>
-    <row r="10" ht="15.75" customHeight="1">
+    <row r="10" spans="1:23" ht="15.75" customHeight="1">
       <c r="A10" s="25"/>
       <c r="B10" s="25"/>
       <c r="C10" s="25"/>
@@ -6850,15 +6591,15 @@
       <c r="V10" s="25"/>
       <c r="W10" s="25"/>
     </row>
-    <row r="11" ht="15.75" customHeight="1">
+    <row r="11" spans="1:23" ht="15.75" customHeight="1">
       <c r="A11" s="25" t="s">
+        <v>235</v>
+      </c>
+      <c r="B11" s="25" t="s">
+        <v>236</v>
+      </c>
+      <c r="C11" s="25" t="s">
         <v>237</v>
-      </c>
-      <c r="B11" s="25" t="s">
-        <v>238</v>
-      </c>
-      <c r="C11" s="25" t="s">
-        <v>239</v>
       </c>
       <c r="D11" s="25"/>
       <c r="E11" s="25"/>
@@ -6881,15 +6622,15 @@
       <c r="V11" s="25"/>
       <c r="W11" s="25"/>
     </row>
-    <row r="12" ht="15.75" customHeight="1">
+    <row r="12" spans="1:23" ht="15.75" customHeight="1">
       <c r="A12" s="25" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="B12" s="25" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C12" s="25" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="D12" s="25"/>
       <c r="E12" s="25"/>
@@ -6912,15 +6653,15 @@
       <c r="V12" s="25"/>
       <c r="W12" s="25"/>
     </row>
-    <row r="13" ht="15.75" customHeight="1">
+    <row r="13" spans="1:23" ht="15.75" customHeight="1">
       <c r="A13" s="25" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="B13" s="25" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="C13" s="25" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="D13" s="25"/>
       <c r="E13" s="25"/>
@@ -6943,15 +6684,15 @@
       <c r="V13" s="25"/>
       <c r="W13" s="25"/>
     </row>
-    <row r="14" ht="15.75" customHeight="1">
+    <row r="14" spans="1:23" ht="15.75" customHeight="1">
       <c r="A14" s="25" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="B14" s="25" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="C14" s="25" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D14" s="25"/>
       <c r="E14" s="25"/>
@@ -6974,15 +6715,15 @@
       <c r="V14" s="25"/>
       <c r="W14" s="25"/>
     </row>
-    <row r="15" ht="15.75" customHeight="1">
+    <row r="15" spans="1:23" ht="15.75" customHeight="1">
       <c r="A15" s="25" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="B15" s="25" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="C15" s="25" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="D15" s="25"/>
       <c r="E15" s="25"/>
@@ -7005,15 +6746,15 @@
       <c r="V15" s="25"/>
       <c r="W15" s="25"/>
     </row>
-    <row r="16" ht="15.75" customHeight="1">
+    <row r="16" spans="1:23" ht="15.75" customHeight="1">
       <c r="A16" s="25" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="B16" s="25" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="C16" s="25" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="D16" s="25"/>
       <c r="E16" s="25"/>
@@ -7036,7 +6777,7 @@
       <c r="V16" s="25"/>
       <c r="W16" s="25"/>
     </row>
-    <row r="17" ht="15.75" customHeight="1">
+    <row r="17" spans="1:23" ht="15.75" customHeight="1">
       <c r="A17" s="25"/>
       <c r="B17" s="25"/>
       <c r="C17" s="25"/>
@@ -7061,15 +6802,15 @@
       <c r="V17" s="25"/>
       <c r="W17" s="25"/>
     </row>
-    <row r="18" ht="15.75" customHeight="1">
+    <row r="18" spans="1:23" ht="15.75" customHeight="1">
       <c r="A18" s="25" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="B18" s="25" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="C18" s="25" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="D18" s="25"/>
       <c r="E18" s="25"/>
@@ -7092,15 +6833,15 @@
       <c r="V18" s="25"/>
       <c r="W18" s="25"/>
     </row>
-    <row r="19" ht="15.75" customHeight="1">
+    <row r="19" spans="1:23" ht="15.75" customHeight="1">
       <c r="A19" s="25" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="B19" s="25" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="C19" s="25" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="D19" s="25"/>
       <c r="E19" s="25"/>
@@ -7123,15 +6864,15 @@
       <c r="V19" s="25"/>
       <c r="W19" s="25"/>
     </row>
-    <row r="20" ht="15.75" customHeight="1">
+    <row r="20" spans="1:23" ht="15.75" customHeight="1">
       <c r="A20" s="25" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="B20" s="25" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="C20" s="25" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="D20" s="25"/>
       <c r="E20" s="25"/>
@@ -7154,15 +6895,15 @@
       <c r="V20" s="25"/>
       <c r="W20" s="25"/>
     </row>
-    <row r="21" ht="15.75" customHeight="1">
+    <row r="21" spans="1:23" ht="15.75" customHeight="1">
       <c r="A21" s="25" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="B21" s="25" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="C21" s="25" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D21" s="25"/>
       <c r="E21" s="25"/>
@@ -7185,15 +6926,15 @@
       <c r="V21" s="25"/>
       <c r="W21" s="25"/>
     </row>
-    <row r="22" ht="15.75" customHeight="1">
+    <row r="22" spans="1:23" ht="15.75" customHeight="1">
       <c r="A22" s="25" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="B22" s="25" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="C22" s="25" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="D22" s="25"/>
       <c r="E22" s="25"/>
@@ -7216,15 +6957,15 @@
       <c r="V22" s="25"/>
       <c r="W22" s="25"/>
     </row>
-    <row r="23" ht="15.75" customHeight="1">
+    <row r="23" spans="1:23" ht="15.75" customHeight="1">
       <c r="A23" s="25" t="s">
+        <v>248</v>
+      </c>
+      <c r="B23" s="25" t="s">
+        <v>249</v>
+      </c>
+      <c r="C23" s="25" t="s">
         <v>250</v>
-      </c>
-      <c r="B23" s="25" t="s">
-        <v>251</v>
-      </c>
-      <c r="C23" s="25" t="s">
-        <v>252</v>
       </c>
       <c r="D23" s="25"/>
       <c r="E23" s="25"/>
@@ -7247,7 +6988,7 @@
       <c r="V23" s="25"/>
       <c r="W23" s="25"/>
     </row>
-    <row r="24" ht="15.75" customHeight="1">
+    <row r="24" spans="1:23" ht="15.75" customHeight="1">
       <c r="A24" s="25"/>
       <c r="B24" s="25"/>
       <c r="C24" s="25"/>
@@ -7272,15 +7013,15 @@
       <c r="V24" s="25"/>
       <c r="W24" s="25"/>
     </row>
-    <row r="25" ht="15.75" customHeight="1">
+    <row r="25" spans="1:23" ht="15.75" customHeight="1">
       <c r="A25" s="25" t="s">
+        <v>251</v>
+      </c>
+      <c r="B25" s="25" t="s">
+        <v>252</v>
+      </c>
+      <c r="C25" s="25" t="s">
         <v>253</v>
-      </c>
-      <c r="B25" s="25" t="s">
-        <v>254</v>
-      </c>
-      <c r="C25" s="25" t="s">
-        <v>255</v>
       </c>
       <c r="D25" s="25"/>
       <c r="E25" s="25"/>
@@ -7303,15 +7044,15 @@
       <c r="V25" s="25"/>
       <c r="W25" s="25"/>
     </row>
-    <row r="26" ht="15.75" customHeight="1">
+    <row r="26" spans="1:23" ht="15.75" customHeight="1">
       <c r="A26" s="25" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="B26" s="25" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C26" s="25" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="D26" s="25"/>
       <c r="E26" s="25"/>
@@ -7334,15 +7075,15 @@
       <c r="V26" s="25"/>
       <c r="W26" s="25"/>
     </row>
-    <row r="27" ht="15.75" customHeight="1">
+    <row r="27" spans="1:23" ht="15.75" customHeight="1">
       <c r="A27" s="25" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="B27" s="25" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C27" s="25" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="D27" s="25"/>
       <c r="E27" s="25"/>
@@ -7365,15 +7106,15 @@
       <c r="V27" s="25"/>
       <c r="W27" s="25"/>
     </row>
-    <row r="28" ht="15.75" customHeight="1">
+    <row r="28" spans="1:23" ht="15.75" customHeight="1">
       <c r="A28" s="25" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="B28" s="25" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="C28" s="25" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D28" s="25"/>
       <c r="E28" s="25"/>
@@ -7396,15 +7137,15 @@
       <c r="V28" s="25"/>
       <c r="W28" s="25"/>
     </row>
-    <row r="29" ht="15.75" customHeight="1">
+    <row r="29" spans="1:23" ht="15.75" customHeight="1">
       <c r="A29" s="25" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="B29" s="25" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="C29" s="25" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D29" s="25"/>
       <c r="E29" s="25"/>
@@ -7427,7 +7168,7 @@
       <c r="V29" s="25"/>
       <c r="W29" s="25"/>
     </row>
-    <row r="30" ht="15.75" customHeight="1">
+    <row r="30" spans="1:23" ht="15.75" customHeight="1">
       <c r="A30" s="25"/>
       <c r="B30" s="25"/>
       <c r="C30" s="25"/>
@@ -7452,15 +7193,15 @@
       <c r="V30" s="25"/>
       <c r="W30" s="25"/>
     </row>
-    <row r="31" ht="15.75" customHeight="1">
+    <row r="31" spans="1:23" ht="15.75" customHeight="1">
       <c r="A31" s="25" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="B31" s="25" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="C31" s="25" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="D31" s="25"/>
       <c r="E31" s="25"/>
@@ -7483,15 +7224,15 @@
       <c r="V31" s="25"/>
       <c r="W31" s="25"/>
     </row>
-    <row r="32" ht="15.75" customHeight="1">
+    <row r="32" spans="1:23" ht="15.75" customHeight="1">
       <c r="A32" s="25" t="s">
+        <v>262</v>
+      </c>
+      <c r="B32" s="25" t="s">
         <v>264</v>
       </c>
-      <c r="B32" s="25" t="s">
-        <v>266</v>
-      </c>
       <c r="C32" s="25" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="D32" s="25"/>
       <c r="E32" s="25"/>
@@ -7514,7 +7255,7 @@
       <c r="V32" s="25"/>
       <c r="W32" s="25"/>
     </row>
-    <row r="33" ht="15.75" customHeight="1">
+    <row r="33" spans="1:23" ht="15.75" customHeight="1">
       <c r="A33" s="25"/>
       <c r="B33" s="25"/>
       <c r="C33" s="25"/>
@@ -7539,170 +7280,170 @@
       <c r="V33" s="25"/>
       <c r="W33" s="25"/>
     </row>
-    <row r="34" ht="15.75" customHeight="1">
+    <row r="34" spans="1:23" ht="15.75" customHeight="1">
       <c r="A34" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="B34" t="str">
         <f t="shared" ref="B34:B47" si="0">SUBSTITUTE(LOWER(SUBSTITUTE(SUBSTITUTE(C34, "(", ""), ")", "")), " ", "_")</f>
         <v>combined_oral_contraceptives</v>
       </c>
       <c r="C34" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="35" ht="15.75" customHeight="1">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="35" spans="1:23" ht="15.75" customHeight="1">
       <c r="A35" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="B35" t="str">
         <f t="shared" si="0"/>
         <v>progesterone_only_pills</v>
       </c>
       <c r="C35" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="36" ht="15.75" customHeight="1">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="36" spans="1:23" ht="15.75" customHeight="1">
       <c r="A36" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="B36" t="str">
         <f t="shared" si="0"/>
         <v>injectibles</v>
       </c>
       <c r="C36" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="37" ht="15.75" customHeight="1">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="37" spans="1:23" ht="15.75" customHeight="1">
       <c r="A37" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="B37" t="str">
         <f t="shared" si="0"/>
         <v>implants_1_rod</v>
       </c>
       <c r="C37" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="38" ht="15.75" customHeight="1">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="38" spans="1:23" ht="15.75" customHeight="1">
       <c r="A38" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="B38" t="str">
         <f t="shared" si="0"/>
         <v>implants_2_rods</v>
       </c>
       <c r="C38" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="39" ht="15.75" customHeight="1">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="39" spans="1:23" ht="15.75" customHeight="1">
       <c r="A39" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="B39" t="str">
         <f t="shared" si="0"/>
         <v>iud</v>
       </c>
       <c r="C39" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="40" ht="15.75" customHeight="1">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="40" spans="1:23" ht="15.75" customHeight="1">
       <c r="A40" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="B40" t="str">
         <f t="shared" si="0"/>
         <v>condoms</v>
       </c>
       <c r="C40" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="41" ht="15.75" customHeight="1">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="41" spans="1:23" ht="15.75" customHeight="1">
       <c r="A41" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="B41" t="str">
         <f t="shared" si="0"/>
         <v>tubal_ligation</v>
       </c>
       <c r="C41" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="42" ht="15.75" customHeight="1">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="42" spans="1:23" ht="15.75" customHeight="1">
       <c r="A42" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="B42" t="str">
         <f t="shared" si="0"/>
         <v>cycle_beads</v>
       </c>
       <c r="C42" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="43" ht="15.75" customHeight="1">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="43" spans="1:23" ht="15.75" customHeight="1">
       <c r="A43" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="B43" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="C43" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="44" ht="15.75" customHeight="1">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="44" spans="1:23" ht="15.75" customHeight="1">
       <c r="B44" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="45" ht="15.75" customHeight="1">
+    <row r="45" spans="1:23" ht="15.75" customHeight="1">
       <c r="A45" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="B45" t="str">
         <f t="shared" si="0"/>
         <v>wants_to_get_pregnant</v>
       </c>
       <c r="C45" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="46" ht="15.75" customHeight="1">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="46" spans="1:23" ht="15.75" customHeight="1">
       <c r="A46" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="B46" t="str">
         <f t="shared" si="0"/>
         <v>did_not_want_fp</v>
       </c>
       <c r="C46" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="47" ht="15.75" customHeight="1">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="47" spans="1:23" ht="15.75" customHeight="1">
       <c r="B47" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
     </row>
-    <row r="48" ht="15.75" customHeight="1">
+    <row r="48" spans="1:23" ht="15.75" customHeight="1">
       <c r="A48" s="24" t="s">
+        <v>278</v>
+      </c>
+      <c r="B48" s="24" t="s">
+        <v>279</v>
+      </c>
+      <c r="C48" s="24" t="s">
         <v>280</v>
-      </c>
-      <c r="B48" s="24" t="s">
-        <v>281</v>
-      </c>
-      <c r="C48" s="24" t="s">
-        <v>282</v>
       </c>
       <c r="D48" s="24"/>
       <c r="E48" s="24"/>
@@ -7725,15 +7466,15 @@
       <c r="V48" s="23"/>
       <c r="W48" s="23"/>
     </row>
-    <row r="49" ht="15.75" customHeight="1">
+    <row r="49" spans="1:23" ht="15.75" customHeight="1">
       <c r="A49" s="24" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="B49" s="24" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="C49" s="24" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="D49" s="24"/>
       <c r="E49" s="24"/>
@@ -7756,237 +7497,237 @@
       <c r="V49" s="23"/>
       <c r="W49" s="23"/>
     </row>
-    <row r="50" ht="15.75" customHeight="1"/>
-    <row r="51" ht="15.75" customHeight="1">
+    <row r="50" spans="1:23" ht="15.75" customHeight="1"/>
+    <row r="51" spans="1:23" ht="15.75" customHeight="1">
       <c r="A51" t="s">
+        <v>283</v>
+      </c>
+      <c r="B51" t="s">
+        <v>284</v>
+      </c>
+      <c r="C51" t="s">
         <v>285</v>
       </c>
-      <c r="B51" t="s">
+    </row>
+    <row r="52" spans="1:23" ht="15.75" customHeight="1">
+      <c r="A52" t="s">
+        <v>283</v>
+      </c>
+      <c r="B52" t="s">
         <v>286</v>
       </c>
-      <c r="C51" t="s">
+      <c r="C52" t="s">
         <v>287</v>
       </c>
     </row>
-    <row r="52" ht="15.75" customHeight="1">
-      <c r="A52" t="s">
-        <v>285</v>
-      </c>
-      <c r="B52" t="s">
+    <row r="53" spans="1:23" ht="15.75" customHeight="1">
+      <c r="A53" t="s">
+        <v>283</v>
+      </c>
+      <c r="B53" t="s">
         <v>288</v>
       </c>
-      <c r="C52" t="s">
+      <c r="C53" t="s">
         <v>289</v>
       </c>
     </row>
-    <row r="53" ht="15.75" customHeight="1">
-      <c r="A53" t="s">
-        <v>285</v>
-      </c>
-      <c r="B53" t="s">
+    <row r="54" spans="1:23" ht="15.75" customHeight="1">
+      <c r="A54" t="s">
+        <v>283</v>
+      </c>
+      <c r="B54" t="s">
         <v>290</v>
       </c>
-      <c r="C53" t="s">
+      <c r="C54" t="s">
         <v>291</v>
       </c>
     </row>
-    <row r="54" ht="15.75" customHeight="1">
-      <c r="A54" t="s">
-        <v>285</v>
-      </c>
-      <c r="B54" t="s">
+    <row r="55" spans="1:23" ht="15.75" customHeight="1">
+      <c r="A55" t="s">
+        <v>283</v>
+      </c>
+      <c r="B55" t="s">
         <v>292</v>
       </c>
-      <c r="C54" t="s">
+      <c r="C55" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="55" ht="15.75" customHeight="1">
-      <c r="A55" t="s">
-        <v>285</v>
-      </c>
-      <c r="B55" t="s">
+    <row r="56" spans="1:23" ht="15.75" customHeight="1">
+      <c r="A56" t="s">
+        <v>283</v>
+      </c>
+      <c r="B56" t="s">
+        <v>260</v>
+      </c>
+      <c r="C56" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="57" spans="1:23" ht="15.75" customHeight="1"/>
+    <row r="58" spans="1:23" ht="15.75" customHeight="1">
+      <c r="A58" s="24" t="s">
         <v>294</v>
       </c>
-      <c r="C55" t="s">
+      <c r="B58" s="24" t="s">
         <v>295</v>
       </c>
-    </row>
-    <row r="56" ht="15.75" customHeight="1">
-      <c r="A56" t="s">
-        <v>285</v>
-      </c>
-      <c r="B56" t="s">
-        <v>262</v>
-      </c>
-      <c r="C56" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="57" ht="15.75" customHeight="1"/>
-    <row r="58" ht="15.75" customHeight="1">
-      <c r="A58" s="24" t="s">
+      <c r="C58" s="24" t="s">
         <v>296</v>
       </c>
-      <c r="B58" s="24" t="s">
+    </row>
+    <row r="59" spans="1:23" ht="15.75" customHeight="1">
+      <c r="A59" s="24" t="s">
+        <v>294</v>
+      </c>
+      <c r="B59" s="24" t="s">
         <v>297</v>
       </c>
-      <c r="C58" s="24" t="s">
+      <c r="C59" s="24" t="s">
         <v>298</v>
       </c>
     </row>
-    <row r="59" ht="15.75" customHeight="1">
-      <c r="A59" s="24" t="s">
-        <v>296</v>
-      </c>
-      <c r="B59" s="24" t="s">
+    <row r="60" spans="1:23" ht="15.75" customHeight="1">
+      <c r="A60" s="24" t="s">
+        <v>294</v>
+      </c>
+      <c r="B60" s="24" t="s">
         <v>299</v>
       </c>
-      <c r="C59" s="24" t="s">
+      <c r="C60" s="24" t="s">
         <v>300</v>
       </c>
     </row>
-    <row r="60" ht="15.75" customHeight="1">
-      <c r="A60" s="24" t="s">
-        <v>296</v>
-      </c>
-      <c r="B60" s="24" t="s">
+    <row r="61" spans="1:23" ht="15.75" customHeight="1">
+      <c r="A61" s="24" t="s">
+        <v>294</v>
+      </c>
+      <c r="B61" s="24" t="s">
+        <v>260</v>
+      </c>
+      <c r="C61" s="24" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="62" spans="1:23" ht="15.75" customHeight="1"/>
+    <row r="63" spans="1:23" ht="15.75" customHeight="1">
+      <c r="A63" s="23" t="s">
         <v>301</v>
       </c>
-      <c r="C60" s="24" t="s">
+      <c r="B63" s="23" t="s">
         <v>302</v>
       </c>
-    </row>
-    <row r="61" ht="15.75" customHeight="1">
-      <c r="A61" s="24" t="s">
-        <v>296</v>
-      </c>
-      <c r="B61" s="24" t="s">
-        <v>262</v>
-      </c>
-      <c r="C61" s="24" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="62" ht="15.75" customHeight="1"/>
-    <row r="63" ht="15.75" customHeight="1">
-      <c r="A63" s="23" t="s">
+      <c r="C63" s="24" t="s">
         <v>303</v>
       </c>
-      <c r="B63" s="23" t="s">
+    </row>
+    <row r="64" spans="1:23" ht="15.75" customHeight="1">
+      <c r="A64" s="23" t="s">
+        <v>301</v>
+      </c>
+      <c r="B64" s="23" t="s">
         <v>304</v>
       </c>
-      <c r="C63" s="24" t="s">
+      <c r="C64" s="24" t="s">
         <v>305</v>
       </c>
     </row>
-    <row r="64" ht="15.75" customHeight="1">
-      <c r="A64" s="23" t="s">
-        <v>303</v>
-      </c>
-      <c r="B64" s="23" t="s">
+    <row r="65" spans="1:3" ht="15.75" customHeight="1">
+      <c r="A65" s="23" t="s">
+        <v>301</v>
+      </c>
+      <c r="B65" s="23" t="s">
         <v>306</v>
       </c>
-      <c r="C64" s="24" t="s">
+      <c r="C65" s="24" t="s">
         <v>307</v>
       </c>
     </row>
-    <row r="65" ht="15.75" customHeight="1">
-      <c r="A65" s="23" t="s">
-        <v>303</v>
-      </c>
-      <c r="B65" s="23" t="s">
+    <row r="66" spans="1:3" ht="15.75" customHeight="1">
+      <c r="A66" s="23" t="s">
+        <v>301</v>
+      </c>
+      <c r="B66" s="23" t="s">
         <v>308</v>
       </c>
-      <c r="C65" s="24" t="s">
+      <c r="C66" s="24" t="s">
         <v>309</v>
       </c>
     </row>
-    <row r="66" ht="15.75" customHeight="1">
-      <c r="A66" s="23" t="s">
-        <v>303</v>
-      </c>
-      <c r="B66" s="23" t="s">
+    <row r="67" spans="1:3" ht="15.75" customHeight="1">
+      <c r="A67" s="23" t="s">
+        <v>301</v>
+      </c>
+      <c r="B67" s="23" t="s">
         <v>310</v>
       </c>
-      <c r="C66" s="24" t="s">
+      <c r="C67" s="24" t="s">
         <v>311</v>
       </c>
     </row>
-    <row r="67" ht="15.75" customHeight="1">
-      <c r="A67" s="23" t="s">
-        <v>303</v>
-      </c>
-      <c r="B67" s="23" t="s">
+    <row r="68" spans="1:3" ht="15.75" customHeight="1"/>
+    <row r="69" spans="1:3" ht="15.75" customHeight="1">
+      <c r="A69" t="s">
         <v>312</v>
       </c>
-      <c r="C67" s="24" t="s">
+      <c r="B69" t="s">
         <v>313</v>
       </c>
-    </row>
-    <row r="68" ht="15.75" customHeight="1"/>
-    <row r="69" ht="15.75" customHeight="1">
-      <c r="A69" t="s">
+      <c r="C69" t="s">
         <v>314</v>
       </c>
-      <c r="B69" t="s">
+    </row>
+    <row r="70" spans="1:3" ht="15.75" customHeight="1">
+      <c r="A70" t="s">
+        <v>312</v>
+      </c>
+      <c r="B70" t="s">
         <v>315</v>
       </c>
-      <c r="C69" t="s">
+      <c r="C70" t="s">
         <v>316</v>
       </c>
     </row>
-    <row r="70" ht="15.75" customHeight="1">
-      <c r="A70" t="s">
-        <v>314</v>
-      </c>
-      <c r="B70" t="s">
+    <row r="71" spans="1:3" ht="15.75" customHeight="1"/>
+    <row r="72" spans="1:3" ht="15.75" customHeight="1">
+      <c r="A72" t="s">
         <v>317</v>
       </c>
-      <c r="C70" t="s">
+      <c r="B72" t="s">
         <v>318</v>
       </c>
-    </row>
-    <row r="71" ht="15.75" customHeight="1"/>
-    <row r="72" ht="15.75" customHeight="1">
-      <c r="A72" t="s">
+      <c r="C72" s="30" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" ht="15.75" customHeight="1">
+      <c r="A73" t="s">
+        <v>317</v>
+      </c>
+      <c r="B73" t="s">
         <v>319</v>
       </c>
-      <c r="B72" t="s">
+      <c r="C73" t="s">
         <v>320</v>
       </c>
-      <c r="C72" s="30" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="73" ht="15.75" customHeight="1">
-      <c r="A73" t="s">
-        <v>319</v>
-      </c>
-      <c r="B73" t="s">
-        <v>321</v>
-      </c>
-      <c r="C73" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="74" ht="15.75" customHeight="1">
+    </row>
+    <row r="74" spans="1:3" ht="15.75" customHeight="1">
       <c r="A74" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="B74" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="C74" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="75" ht="15.75" customHeight="1"/>
-    <row r="76" ht="15.75" customHeight="1"/>
-    <row r="77" ht="15.75" customHeight="1"/>
-    <row r="78" ht="15.75" customHeight="1"/>
-    <row r="79" ht="15.75" customHeight="1"/>
-    <row r="80" ht="15.75" customHeight="1"/>
+        <v>261</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" ht="15.75" customHeight="1"/>
+    <row r="76" spans="1:3" ht="15.75" customHeight="1"/>
+    <row r="77" spans="1:3" ht="15.75" customHeight="1"/>
+    <row r="78" spans="1:3" ht="15.75" customHeight="1"/>
+    <row r="79" spans="1:3" ht="15.75" customHeight="1"/>
+    <row r="80" spans="1:3" ht="15.75" customHeight="1"/>
     <row r="81" ht="15.75" customHeight="1"/>
     <row r="82" ht="15.75" customHeight="1"/>
     <row r="83" ht="15.75" customHeight="1"/>
@@ -8908,9 +8649,7 @@
     <row r="999" ht="15.75" customHeight="1"/>
     <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
-  <printOptions headings="0" gridLines="0"/>
-  <pageMargins left="0.70078740157480324" right="0.70078740157480324" top="0.75196850393700787" bottom="0.75196850393700787" header="0.29999999999999999" footer="0.29999999999999999"/>
-  <pageSetup paperSize="9" scale="100" firstPageNumber="2147483648" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
-  <headerFooter/>
+  <pageMargins left="0.70078740157480324" right="0.70078740157480324" top="0.75196850393700787" bottom="0.75196850393700787" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" firstPageNumber="2147483648" orientation="portrait"/>
 </worksheet>
 </file>